--- a/research/traditional_assets/database/data/new_zealand/new_zealand_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_cable_tv.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07143251743292804</v>
+        <v>0.07126490638411584</v>
       </c>
       <c r="C2">
-        <v>214.0313529047654</v>
+        <v>212.1857614506239</v>
       </c>
       <c r="D2">
-        <v>191.0313529047654</v>
+        <v>191.3407614506239</v>
       </c>
       <c r="E2">
-        <v>-15</v>
+        <v>-12.845</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.155</v>
       </c>
       <c r="G2">
         <v>23</v>
@@ -1451,28 +1451,28 @@
         <v>13</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1083965</v>
       </c>
       <c r="N2">
-        <v>13</v>
+        <v>12.8916035</v>
       </c>
       <c r="O2">
-        <v>3.640000000000001</v>
+        <v>3.609648980000001</v>
       </c>
       <c r="P2">
-        <v>9.359999999999999</v>
+        <v>9.281954519999999</v>
       </c>
       <c r="Q2">
-        <v>59.36</v>
+        <v>59.28195452</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07143251743292804</v>
+        <v>0.07161893574153115</v>
       </c>
       <c r="T2">
-        <v>0.5919749984509941</v>
+        <v>0.5962802711670013</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.9300715429004</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07126490638411584</v>
+        <v>0.07109729533530364</v>
       </c>
       <c r="C3">
-        <v>212.1857614506239</v>
+        <v>210.3411739045389</v>
       </c>
       <c r="D3">
-        <v>191.3407614506239</v>
+        <v>191.6511739045389</v>
       </c>
       <c r="E3">
-        <v>-12.845</v>
+        <v>-10.69</v>
       </c>
       <c r="F3">
-        <v>2.155</v>
+        <v>4.31</v>
       </c>
       <c r="G3">
         <v>23</v>
@@ -1533,28 +1533,28 @@
         <v>13</v>
       </c>
       <c r="M3">
-        <v>0.1083965</v>
+        <v>0.216793</v>
       </c>
       <c r="N3">
-        <v>12.8916035</v>
+        <v>12.783207</v>
       </c>
       <c r="O3">
-        <v>3.609648980000001</v>
+        <v>3.579297960000001</v>
       </c>
       <c r="P3">
-        <v>9.281954519999999</v>
+        <v>9.203909039999999</v>
       </c>
       <c r="Q3">
-        <v>59.28195452</v>
+        <v>59.20390904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07161893574153115</v>
+        <v>0.07180915850541188</v>
       </c>
       <c r="T3">
-        <v>0.5962802711670013</v>
+        <v>0.6006734065914985</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.9300715429004</v>
+        <v>59.96503577145018</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07109729533530364</v>
+        <v>0.07092968428649145</v>
       </c>
       <c r="C4">
-        <v>210.3411739045389</v>
+        <v>208.4975951603752</v>
       </c>
       <c r="D4">
-        <v>191.6511739045389</v>
+        <v>191.9625951603752</v>
       </c>
       <c r="E4">
-        <v>-10.69</v>
+        <v>-8.535</v>
       </c>
       <c r="F4">
-        <v>4.31</v>
+        <v>6.465</v>
       </c>
       <c r="G4">
         <v>23</v>
@@ -1615,28 +1615,28 @@
         <v>13</v>
       </c>
       <c r="M4">
-        <v>0.216793</v>
+        <v>0.3251895</v>
       </c>
       <c r="N4">
-        <v>12.783207</v>
+        <v>12.6748105</v>
       </c>
       <c r="O4">
-        <v>3.579297960000001</v>
+        <v>3.54894694</v>
       </c>
       <c r="P4">
-        <v>9.203909039999999</v>
+        <v>9.125863559999999</v>
       </c>
       <c r="Q4">
-        <v>59.20390904</v>
+        <v>59.12586356</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07180915850541188</v>
+        <v>0.07200330338813551</v>
       </c>
       <c r="T4">
-        <v>0.6006734065914985</v>
+        <v>0.605157122127841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.96503577145018</v>
+        <v>39.97669051430012</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07092968428649145</v>
+        <v>0.07076207323767925</v>
       </c>
       <c r="C5">
-        <v>208.4975951603752</v>
+        <v>206.6550301438582</v>
       </c>
       <c r="D5">
-        <v>191.9625951603752</v>
+        <v>192.2750301438582</v>
       </c>
       <c r="E5">
-        <v>-8.535</v>
+        <v>-6.379999999999999</v>
       </c>
       <c r="F5">
-        <v>6.465</v>
+        <v>8.620000000000001</v>
       </c>
       <c r="G5">
         <v>23</v>
@@ -1697,28 +1697,28 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <v>0.3251895</v>
+        <v>0.433586</v>
       </c>
       <c r="N5">
-        <v>12.6748105</v>
+        <v>12.566414</v>
       </c>
       <c r="O5">
-        <v>3.54894694</v>
+        <v>3.518595920000001</v>
       </c>
       <c r="P5">
-        <v>9.125863559999999</v>
+        <v>9.047818079999999</v>
       </c>
       <c r="Q5">
-        <v>59.12586356</v>
+        <v>59.04781808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07200330338813551</v>
+        <v>0.07220149295591588</v>
       </c>
       <c r="T5">
-        <v>0.605157122127841</v>
+        <v>0.6097342484045239</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.97669051430012</v>
+        <v>29.98251788572509</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07076207323767925</v>
+        <v>0.07059446218886704</v>
       </c>
       <c r="C6">
-        <v>206.6550301438582</v>
+        <v>204.8134838128337</v>
       </c>
       <c r="D6">
-        <v>192.2750301438582</v>
+        <v>192.5884838128337</v>
       </c>
       <c r="E6">
-        <v>-6.379999999999999</v>
+        <v>-4.225</v>
       </c>
       <c r="F6">
-        <v>8.620000000000001</v>
+        <v>10.775</v>
       </c>
       <c r="G6">
         <v>23</v>
@@ -1779,28 +1779,28 @@
         <v>13</v>
       </c>
       <c r="M6">
-        <v>0.433586</v>
+        <v>0.5419825</v>
       </c>
       <c r="N6">
-        <v>12.566414</v>
+        <v>12.4580175</v>
       </c>
       <c r="O6">
-        <v>3.518595920000001</v>
+        <v>3.488244900000001</v>
       </c>
       <c r="P6">
-        <v>9.047818079999999</v>
+        <v>8.969772599999999</v>
       </c>
       <c r="Q6">
-        <v>59.04781808</v>
+        <v>58.9697726</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07220149295591588</v>
+        <v>0.07240385493564952</v>
       </c>
       <c r="T6">
-        <v>0.6097342484045239</v>
+        <v>0.6144077352344002</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.98251788572509</v>
+        <v>23.98601430858007</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07059446218886704</v>
+        <v>0.07042685114005484</v>
       </c>
       <c r="C7">
-        <v>204.8134838128337</v>
+        <v>202.9729611575301</v>
       </c>
       <c r="D7">
-        <v>192.5884838128337</v>
+        <v>192.9029611575301</v>
       </c>
       <c r="E7">
-        <v>-4.225</v>
+        <v>-2.069999999999999</v>
       </c>
       <c r="F7">
-        <v>10.775</v>
+        <v>12.93</v>
       </c>
       <c r="G7">
         <v>23</v>
@@ -1861,28 +1861,28 @@
         <v>13</v>
       </c>
       <c r="M7">
-        <v>0.5419825</v>
+        <v>0.650379</v>
       </c>
       <c r="N7">
-        <v>12.4580175</v>
+        <v>12.349621</v>
       </c>
       <c r="O7">
-        <v>3.488244900000001</v>
+        <v>3.45789388</v>
       </c>
       <c r="P7">
-        <v>8.969772599999999</v>
+        <v>8.891727119999999</v>
       </c>
       <c r="Q7">
-        <v>58.9697726</v>
+        <v>58.89172712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07240385493564952</v>
+        <v>0.07261052248942004</v>
       </c>
       <c r="T7">
-        <v>0.6144077352344002</v>
+        <v>0.6191806579542738</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.98601430858007</v>
+        <v>19.98834525715006</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07042685114005484</v>
+        <v>0.07025924009124265</v>
       </c>
       <c r="C8">
-        <v>202.9729611575301</v>
+        <v>201.1334672008233</v>
       </c>
       <c r="D8">
-        <v>192.9029611575301</v>
+        <v>193.2184672008233</v>
       </c>
       <c r="E8">
-        <v>-2.07</v>
+        <v>0.08499999999999908</v>
       </c>
       <c r="F8">
-        <v>12.93</v>
+        <v>15.085</v>
       </c>
       <c r="G8">
         <v>23</v>
@@ -1943,28 +1943,28 @@
         <v>13</v>
       </c>
       <c r="M8">
-        <v>0.6503789999999999</v>
+        <v>0.7587754999999999</v>
       </c>
       <c r="N8">
-        <v>12.349621</v>
+        <v>12.2412245</v>
       </c>
       <c r="O8">
-        <v>3.457893880000001</v>
+        <v>3.42754286</v>
       </c>
       <c r="P8">
-        <v>8.891727120000001</v>
+        <v>8.813681639999999</v>
       </c>
       <c r="Q8">
-        <v>58.89172712</v>
+        <v>58.81368164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07261052248942004</v>
+        <v>0.07282163450671253</v>
       </c>
       <c r="T8">
-        <v>0.6191806579542738</v>
+        <v>0.6240562241734996</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.98834525715007</v>
+        <v>17.13286736327148</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07025924009124265</v>
+        <v>0.07009162904243045</v>
       </c>
       <c r="C9">
-        <v>201.1334672008233</v>
+        <v>199.2950069985041</v>
       </c>
       <c r="D9">
-        <v>193.2184672008233</v>
+        <v>193.5350069985041</v>
       </c>
       <c r="E9">
-        <v>0.08500000000000085</v>
+        <v>2.240000000000002</v>
       </c>
       <c r="F9">
-        <v>15.085</v>
+        <v>17.24</v>
       </c>
       <c r="G9">
         <v>23</v>
@@ -2025,28 +2025,28 @@
         <v>13</v>
       </c>
       <c r="M9">
-        <v>0.7587755</v>
+        <v>0.8671720000000001</v>
       </c>
       <c r="N9">
-        <v>12.2412245</v>
+        <v>12.132828</v>
       </c>
       <c r="O9">
-        <v>3.42754286</v>
+        <v>3.397191840000001</v>
       </c>
       <c r="P9">
-        <v>8.813681639999999</v>
+        <v>8.735636159999999</v>
       </c>
       <c r="Q9">
-        <v>58.81368164</v>
+        <v>58.73563616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07282163450671253</v>
+        <v>0.07303733591568527</v>
       </c>
       <c r="T9">
-        <v>0.6240562241734996</v>
+        <v>0.6290377809627085</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.13286736327148</v>
+        <v>14.99125894286255</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07009162904243045</v>
+        <v>0.06992401799361825</v>
       </c>
       <c r="C10">
-        <v>199.2950069985041</v>
+        <v>197.4575856395481</v>
       </c>
       <c r="D10">
-        <v>193.5350069985041</v>
+        <v>193.8525856395481</v>
       </c>
       <c r="E10">
-        <v>2.240000000000002</v>
+        <v>4.395</v>
       </c>
       <c r="F10">
-        <v>17.24</v>
+        <v>19.395</v>
       </c>
       <c r="G10">
         <v>23</v>
@@ -2107,28 +2107,28 @@
         <v>13</v>
       </c>
       <c r="M10">
-        <v>0.8671720000000001</v>
+        <v>0.9755684999999999</v>
       </c>
       <c r="N10">
-        <v>12.132828</v>
+        <v>12.0244315</v>
       </c>
       <c r="O10">
-        <v>3.397191840000001</v>
+        <v>3.366840820000001</v>
       </c>
       <c r="P10">
-        <v>8.735636159999999</v>
+        <v>8.65759068</v>
       </c>
       <c r="Q10">
-        <v>58.73563616</v>
+        <v>58.65759068</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07303733591568527</v>
+        <v>0.07325777801496511</v>
       </c>
       <c r="T10">
-        <v>0.6290377809627085</v>
+        <v>0.6341288225165155</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.99125894286255</v>
+        <v>13.32556350476671</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06992401799361825</v>
+        <v>0.06986440694480606</v>
       </c>
       <c r="C11">
-        <v>197.4575856395481</v>
+        <v>195.4157842248962</v>
       </c>
       <c r="D11">
-        <v>193.8525856395481</v>
+        <v>193.9657842248962</v>
       </c>
       <c r="E11">
-        <v>4.395</v>
+        <v>6.549999999999997</v>
       </c>
       <c r="F11">
-        <v>19.395</v>
+        <v>21.55</v>
       </c>
       <c r="G11">
         <v>23</v>
@@ -2189,45 +2189,45 @@
         <v>13</v>
       </c>
       <c r="M11">
-        <v>0.9755684999999999</v>
+        <v>1.11629</v>
       </c>
       <c r="N11">
-        <v>12.0244315</v>
+        <v>11.88371</v>
       </c>
       <c r="O11">
-        <v>3.366840820000001</v>
+        <v>3.3274388</v>
       </c>
       <c r="P11">
-        <v>8.65759068</v>
+        <v>8.556271200000001</v>
       </c>
       <c r="Q11">
-        <v>58.65759068</v>
+        <v>58.5562712</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07325777801496511</v>
+        <v>0.07348311882756228</v>
       </c>
       <c r="T11">
-        <v>0.6341288225165155</v>
+        <v>0.6393329983270737</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.32556350476671</v>
+        <v>11.64571930233183</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06986440694480606</v>
+        <v>0.06970759589599386</v>
       </c>
       <c r="C12">
-        <v>195.4157842248962</v>
+        <v>193.5591933208862</v>
       </c>
       <c r="D12">
-        <v>193.9657842248962</v>
+        <v>194.2641933208862</v>
       </c>
       <c r="E12">
-        <v>6.550000000000001</v>
+        <v>8.705000000000002</v>
       </c>
       <c r="F12">
-        <v>21.55</v>
+        <v>23.705</v>
       </c>
       <c r="G12">
         <v>23</v>
@@ -2271,28 +2271,28 @@
         <v>13</v>
       </c>
       <c r="M12">
-        <v>1.11629</v>
+        <v>1.227919</v>
       </c>
       <c r="N12">
-        <v>11.88371</v>
+        <v>11.772081</v>
       </c>
       <c r="O12">
-        <v>3.3274388</v>
+        <v>3.29618268</v>
       </c>
       <c r="P12">
-        <v>8.556271200000001</v>
+        <v>8.475898319999999</v>
       </c>
       <c r="Q12">
-        <v>58.5562712</v>
+        <v>58.47589832</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07348311882756228</v>
+        <v>0.07371352347864478</v>
       </c>
       <c r="T12">
-        <v>0.6393329983270737</v>
+        <v>0.6446541219086556</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.64571930233183</v>
+        <v>10.58701754757439</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06970759589599386</v>
+        <v>0.06969766484718166</v>
       </c>
       <c r="C13">
-        <v>193.5591933208862</v>
+        <v>191.4231228784283</v>
       </c>
       <c r="D13">
-        <v>194.2641933208862</v>
+        <v>194.2831228784283</v>
       </c>
       <c r="E13">
-        <v>8.705000000000002</v>
+        <v>10.86</v>
       </c>
       <c r="F13">
-        <v>23.705</v>
+        <v>25.86</v>
       </c>
       <c r="G13">
         <v>23</v>
@@ -2353,45 +2353,45 @@
         <v>13</v>
       </c>
       <c r="M13">
-        <v>1.227919</v>
+        <v>1.38351</v>
       </c>
       <c r="N13">
-        <v>11.772081</v>
+        <v>11.61649</v>
       </c>
       <c r="O13">
-        <v>3.29618268</v>
+        <v>3.2526172</v>
       </c>
       <c r="P13">
-        <v>8.475898319999999</v>
+        <v>8.363872799999999</v>
       </c>
       <c r="Q13">
-        <v>58.47589832</v>
+        <v>58.3638728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07371352347864478</v>
+        <v>0.07394916459907007</v>
       </c>
       <c r="T13">
-        <v>0.6446541219086556</v>
+        <v>0.6500961801170917</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.58701754757439</v>
+        <v>9.396390340510731</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06969766484718166</v>
+        <v>0.06955309379836945</v>
       </c>
       <c r="C14">
-        <v>191.4231228784283</v>
+        <v>189.5441078827639</v>
       </c>
       <c r="D14">
-        <v>194.2831228784283</v>
+        <v>194.5591078827639</v>
       </c>
       <c r="E14">
-        <v>10.86</v>
+        <v>13.015</v>
       </c>
       <c r="F14">
-        <v>25.86</v>
+        <v>28.015</v>
       </c>
       <c r="G14">
         <v>23</v>
@@ -2435,28 +2435,28 @@
         <v>13</v>
       </c>
       <c r="M14">
-        <v>1.38351</v>
+        <v>1.4988025</v>
       </c>
       <c r="N14">
-        <v>11.61649</v>
+        <v>11.5011975</v>
       </c>
       <c r="O14">
-        <v>3.2526172</v>
+        <v>3.2203353</v>
       </c>
       <c r="P14">
-        <v>8.363872799999999</v>
+        <v>8.2808622</v>
       </c>
       <c r="Q14">
-        <v>58.3638728</v>
+        <v>58.2808622</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07394916459907007</v>
+        <v>0.0741902227567465</v>
       </c>
       <c r="T14">
-        <v>0.6500961801170917</v>
+        <v>0.6556633431119285</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.396390340510731</v>
+        <v>8.673591083548366</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06955309379836945</v>
+        <v>0.06940852274955726</v>
       </c>
       <c r="C15">
-        <v>189.5441078827639</v>
+        <v>187.6658780924631</v>
       </c>
       <c r="D15">
-        <v>194.5591078827639</v>
+        <v>194.8358780924631</v>
       </c>
       <c r="E15">
-        <v>13.015</v>
+        <v>15.17</v>
       </c>
       <c r="F15">
-        <v>28.015</v>
+        <v>30.17</v>
       </c>
       <c r="G15">
         <v>23</v>
@@ -2517,28 +2517,28 @@
         <v>13</v>
       </c>
       <c r="M15">
-        <v>1.4988025</v>
+        <v>1.614095</v>
       </c>
       <c r="N15">
-        <v>11.5011975</v>
+        <v>11.385905</v>
       </c>
       <c r="O15">
-        <v>3.2203353</v>
+        <v>3.1880534</v>
       </c>
       <c r="P15">
-        <v>8.2808622</v>
+        <v>8.1978516</v>
       </c>
       <c r="Q15">
-        <v>58.2808622</v>
+        <v>58.1978516</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0741902227567465</v>
+        <v>0.07443688691808983</v>
       </c>
       <c r="T15">
-        <v>0.6556633431119285</v>
+        <v>0.6613599750136222</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.673591083548366</v>
+        <v>8.054048863294911</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06940852274955726</v>
+        <v>0.06935035170074506</v>
       </c>
       <c r="C16">
-        <v>187.6658780924631</v>
+        <v>185.62246440595</v>
       </c>
       <c r="D16">
-        <v>194.8358780924631</v>
+        <v>194.9474644059501</v>
       </c>
       <c r="E16">
-        <v>15.17</v>
+        <v>17.325</v>
       </c>
       <c r="F16">
-        <v>30.17</v>
+        <v>32.325</v>
       </c>
       <c r="G16">
         <v>23</v>
@@ -2599,45 +2599,45 @@
         <v>13</v>
       </c>
       <c r="M16">
-        <v>1.614095</v>
+        <v>1.7552475</v>
       </c>
       <c r="N16">
-        <v>11.385905</v>
+        <v>11.2447525</v>
       </c>
       <c r="O16">
-        <v>3.1880534</v>
+        <v>3.148530700000001</v>
       </c>
       <c r="P16">
-        <v>8.1978516</v>
+        <v>8.0962218</v>
       </c>
       <c r="Q16">
-        <v>58.1978516</v>
+        <v>58.0962218</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07443688691808983</v>
+        <v>0.07468935494205302</v>
       </c>
       <c r="T16">
-        <v>0.6613599750136222</v>
+        <v>0.6671906453130028</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.054048863294911</v>
+        <v>7.406362920328899</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06935035170074506</v>
+        <v>0.06921154065193287</v>
       </c>
       <c r="C17">
-        <v>185.6224644059501</v>
+        <v>183.734255093427</v>
       </c>
       <c r="D17">
-        <v>194.9474644059501</v>
+        <v>195.2142550934269</v>
       </c>
       <c r="E17">
-        <v>17.325</v>
+        <v>19.48</v>
       </c>
       <c r="F17">
-        <v>32.325</v>
+        <v>34.48</v>
       </c>
       <c r="G17">
         <v>23</v>
@@ -2681,28 +2681,28 @@
         <v>13</v>
       </c>
       <c r="M17">
-        <v>1.7552475</v>
+        <v>1.872264</v>
       </c>
       <c r="N17">
-        <v>11.2447525</v>
+        <v>11.127736</v>
       </c>
       <c r="O17">
-        <v>3.148530700000001</v>
+        <v>3.115766080000001</v>
       </c>
       <c r="P17">
-        <v>8.0962218</v>
+        <v>8.01196992</v>
       </c>
       <c r="Q17">
-        <v>58.0962218</v>
+        <v>58.01196992</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07468935494205302</v>
+        <v>0.07494783410944389</v>
       </c>
       <c r="T17">
-        <v>0.6671906453130028</v>
+        <v>0.6731601410957019</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.406362920328901</v>
+        <v>6.943465237808343</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06921154065193287</v>
+        <v>0.06907272960312066</v>
       </c>
       <c r="C18">
-        <v>183.734255093427</v>
+        <v>181.846777001621</v>
       </c>
       <c r="D18">
-        <v>195.2142550934269</v>
+        <v>195.481777001621</v>
       </c>
       <c r="E18">
-        <v>19.48</v>
+        <v>21.63500000000001</v>
       </c>
       <c r="F18">
-        <v>34.48</v>
+        <v>36.63500000000001</v>
       </c>
       <c r="G18">
         <v>23</v>
@@ -2763,28 +2763,28 @@
         <v>13</v>
       </c>
       <c r="M18">
-        <v>1.872264</v>
+        <v>1.9892805</v>
       </c>
       <c r="N18">
-        <v>11.127736</v>
+        <v>11.0107195</v>
       </c>
       <c r="O18">
-        <v>3.115766080000001</v>
+        <v>3.083001460000001</v>
       </c>
       <c r="P18">
-        <v>8.01196992</v>
+        <v>7.92771804</v>
       </c>
       <c r="Q18">
-        <v>58.01196992</v>
+        <v>57.92771804</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07494783410944389</v>
+        <v>0.07521254169050683</v>
       </c>
       <c r="T18">
-        <v>0.6731601410957019</v>
+        <v>0.6792734801502732</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.943465237808343</v>
+        <v>6.535026106172558</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06907272960312066</v>
+        <v>0.06893391855430847</v>
       </c>
       <c r="C19">
-        <v>181.846777001621</v>
+        <v>179.9600331408554</v>
       </c>
       <c r="D19">
-        <v>195.481777001621</v>
+        <v>195.7500331408554</v>
       </c>
       <c r="E19">
-        <v>21.63500000000001</v>
+        <v>23.79000000000001</v>
       </c>
       <c r="F19">
-        <v>36.63500000000001</v>
+        <v>38.79000000000001</v>
       </c>
       <c r="G19">
         <v>23</v>
@@ -2845,28 +2845,28 @@
         <v>13</v>
       </c>
       <c r="M19">
-        <v>1.9892805</v>
+        <v>2.106297000000001</v>
       </c>
       <c r="N19">
-        <v>11.0107195</v>
+        <v>10.893703</v>
       </c>
       <c r="O19">
-        <v>3.083001460000001</v>
+        <v>3.05023684</v>
       </c>
       <c r="P19">
-        <v>7.92771804</v>
+        <v>7.843466159999998</v>
       </c>
       <c r="Q19">
-        <v>57.92771804</v>
+        <v>57.84346616</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07521254169050683</v>
+        <v>0.07548370555403472</v>
       </c>
       <c r="T19">
-        <v>0.6792734801502732</v>
+        <v>0.6855359250354438</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.535026106172558</v>
+        <v>6.171969100274081</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06893391855430847</v>
+        <v>0.06893190750549627</v>
       </c>
       <c r="C20">
-        <v>179.9600331408554</v>
+        <v>177.8089249581759</v>
       </c>
       <c r="D20">
-        <v>195.7500331408554</v>
+        <v>195.7539249581758</v>
       </c>
       <c r="E20">
-        <v>23.79</v>
+        <v>25.945</v>
       </c>
       <c r="F20">
-        <v>38.79</v>
+        <v>40.945</v>
       </c>
       <c r="G20">
         <v>23</v>
@@ -2927,45 +2927,45 @@
         <v>13</v>
       </c>
       <c r="M20">
-        <v>2.106297</v>
+        <v>2.2642585</v>
       </c>
       <c r="N20">
-        <v>10.893703</v>
+        <v>10.7357415</v>
       </c>
       <c r="O20">
-        <v>3.05023684</v>
+        <v>3.00600762</v>
       </c>
       <c r="P20">
-        <v>7.84346616</v>
+        <v>7.72973388</v>
       </c>
       <c r="Q20">
-        <v>57.84346616</v>
+        <v>57.72973388</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07548370555403472</v>
+        <v>0.07576156482160033</v>
       </c>
       <c r="T20">
-        <v>0.6855359250354438</v>
+        <v>0.6919529981893842</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.28</v>
       </c>
       <c r="W20">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.171969100274083</v>
+        <v>5.741393926532681</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06893190750549627</v>
+        <v>0.06880029645668408</v>
       </c>
       <c r="C21">
-        <v>177.8089249581759</v>
+        <v>175.9089578879912</v>
       </c>
       <c r="D21">
-        <v>195.7539249581758</v>
+        <v>196.0089578879912</v>
       </c>
       <c r="E21">
-        <v>25.945</v>
+        <v>28.1</v>
       </c>
       <c r="F21">
-        <v>40.945</v>
+        <v>43.1</v>
       </c>
       <c r="G21">
         <v>23</v>
@@ -3009,28 +3009,28 @@
         <v>13</v>
       </c>
       <c r="M21">
-        <v>2.2642585</v>
+        <v>2.38343</v>
       </c>
       <c r="N21">
-        <v>10.7357415</v>
+        <v>10.61657</v>
       </c>
       <c r="O21">
-        <v>3.00600762</v>
+        <v>2.9726396</v>
       </c>
       <c r="P21">
-        <v>7.72973388</v>
+        <v>7.643930399999999</v>
       </c>
       <c r="Q21">
-        <v>57.72973388</v>
+        <v>57.6439304</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07576156482160033</v>
+        <v>0.07604637057085509</v>
       </c>
       <c r="T21">
-        <v>0.6919529981893842</v>
+        <v>0.6985304981721731</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.741393926532681</v>
+        <v>5.454324230206047</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06880029645668408</v>
+        <v>0.06866868540787187</v>
       </c>
       <c r="C22">
-        <v>175.9089578879912</v>
+        <v>174.0096562107877</v>
       </c>
       <c r="D22">
-        <v>196.0089578879912</v>
+        <v>196.2646562107876</v>
       </c>
       <c r="E22">
-        <v>28.1</v>
+        <v>30.255</v>
       </c>
       <c r="F22">
-        <v>43.1</v>
+        <v>45.255</v>
       </c>
       <c r="G22">
         <v>23</v>
@@ -3091,28 +3091,28 @@
         <v>13</v>
       </c>
       <c r="M22">
-        <v>2.38343</v>
+        <v>2.5026015</v>
       </c>
       <c r="N22">
-        <v>10.61657</v>
+        <v>10.4973985</v>
       </c>
       <c r="O22">
-        <v>2.9726396</v>
+        <v>2.93927158</v>
       </c>
       <c r="P22">
-        <v>7.643930399999999</v>
+        <v>7.558126919999999</v>
       </c>
       <c r="Q22">
-        <v>57.6439304</v>
+        <v>57.55812692</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07604637057085509</v>
+        <v>0.07633838659224287</v>
       </c>
       <c r="T22">
-        <v>0.6985304981721731</v>
+        <v>0.705274517141868</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.454324230206047</v>
+        <v>5.19459450495814</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06866868540787187</v>
+        <v>0.06853707435905967</v>
       </c>
       <c r="C23">
-        <v>174.0096562107877</v>
+        <v>172.1110225340295</v>
       </c>
       <c r="D23">
-        <v>196.2646562107876</v>
+        <v>196.5210225340295</v>
       </c>
       <c r="E23">
-        <v>30.255</v>
+        <v>32.41</v>
       </c>
       <c r="F23">
-        <v>45.255</v>
+        <v>47.41</v>
       </c>
       <c r="G23">
         <v>23</v>
@@ -3173,28 +3173,28 @@
         <v>13</v>
       </c>
       <c r="M23">
-        <v>2.5026015</v>
+        <v>2.621773</v>
       </c>
       <c r="N23">
-        <v>10.4973985</v>
+        <v>10.378227</v>
       </c>
       <c r="O23">
-        <v>2.93927158</v>
+        <v>2.90590356</v>
       </c>
       <c r="P23">
-        <v>7.558126919999999</v>
+        <v>7.472323439999998</v>
       </c>
       <c r="Q23">
-        <v>57.55812692</v>
+        <v>57.47232344</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07633838659224287</v>
+        <v>0.07663789020392266</v>
       </c>
       <c r="T23">
-        <v>0.705274517141868</v>
+        <v>0.7121914596748884</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.194594504958141</v>
+        <v>4.958476572914588</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06853707435905967</v>
+        <v>0.06840546331024748</v>
       </c>
       <c r="C24">
-        <v>172.1110225340295</v>
+        <v>170.2130594788223</v>
       </c>
       <c r="D24">
-        <v>196.5210225340295</v>
+        <v>196.7780594788223</v>
       </c>
       <c r="E24">
-        <v>32.41</v>
+        <v>34.565</v>
       </c>
       <c r="F24">
-        <v>47.41</v>
+        <v>49.565</v>
       </c>
       <c r="G24">
         <v>23</v>
@@ -3255,28 +3255,28 @@
         <v>13</v>
       </c>
       <c r="M24">
-        <v>2.621773</v>
+        <v>2.7409445</v>
       </c>
       <c r="N24">
-        <v>10.378227</v>
+        <v>10.2590555</v>
       </c>
       <c r="O24">
-        <v>2.90590356</v>
+        <v>2.87253554</v>
       </c>
       <c r="P24">
-        <v>7.472323439999998</v>
+        <v>7.386519959999999</v>
       </c>
       <c r="Q24">
-        <v>57.47232344</v>
+        <v>57.38651996</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07663789020392266</v>
+        <v>0.07694517313019153</v>
       </c>
       <c r="T24">
-        <v>0.7121914596748884</v>
+        <v>0.7192880630529221</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.958476572914588</v>
+        <v>4.74289063496178</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06840546331024748</v>
+        <v>0.06827385226143529</v>
       </c>
       <c r="C25">
-        <v>170.2130594788223</v>
+        <v>168.3157696800029</v>
       </c>
       <c r="D25">
-        <v>196.7780594788223</v>
+        <v>197.0357696800029</v>
       </c>
       <c r="E25">
-        <v>34.565</v>
+        <v>36.72000000000001</v>
       </c>
       <c r="F25">
-        <v>49.565</v>
+        <v>51.72000000000001</v>
       </c>
       <c r="G25">
         <v>23</v>
@@ -3337,28 +3337,28 @@
         <v>13</v>
       </c>
       <c r="M25">
-        <v>2.7409445</v>
+        <v>2.860116000000001</v>
       </c>
       <c r="N25">
-        <v>10.2590555</v>
+        <v>10.139884</v>
       </c>
       <c r="O25">
-        <v>2.87253554</v>
+        <v>2.83916752</v>
       </c>
       <c r="P25">
-        <v>7.386519959999999</v>
+        <v>7.300716479999998</v>
       </c>
       <c r="Q25">
-        <v>57.38651996</v>
+        <v>57.30071648</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07694517313019153</v>
+        <v>0.07726054244925695</v>
       </c>
       <c r="T25">
-        <v>0.7192880630529221</v>
+        <v>0.7265714191514308</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.74289063496178</v>
+        <v>4.545270191838371</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06827385226143529</v>
+        <v>0.06859224121262307</v>
       </c>
       <c r="C26">
-        <v>168.3157696800029</v>
+        <v>165.538481047746</v>
       </c>
       <c r="D26">
-        <v>197.0357696800029</v>
+        <v>196.413481047746</v>
       </c>
       <c r="E26">
-        <v>36.72</v>
+        <v>38.875</v>
       </c>
       <c r="F26">
-        <v>51.72</v>
+        <v>53.875</v>
       </c>
       <c r="G26">
         <v>23</v>
@@ -3419,45 +3419,45 @@
         <v>13</v>
       </c>
       <c r="M26">
-        <v>2.860116</v>
+        <v>3.113975</v>
       </c>
       <c r="N26">
-        <v>10.139884</v>
+        <v>9.886025</v>
       </c>
       <c r="O26">
-        <v>2.83916752</v>
+        <v>2.768087</v>
       </c>
       <c r="P26">
-        <v>7.30071648</v>
+        <v>7.117938</v>
       </c>
       <c r="Q26">
-        <v>57.30071648</v>
+        <v>57.117938</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07726054244925695</v>
+        <v>0.07758432161683076</v>
       </c>
       <c r="T26">
-        <v>0.7265714191514308</v>
+        <v>0.7340489980792327</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.545270191838373</v>
+        <v>4.174728441943175</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06859224121262307</v>
+        <v>0.06847863016381088</v>
       </c>
       <c r="C27">
-        <v>165.538481047746</v>
+        <v>163.6050813639692</v>
       </c>
       <c r="D27">
-        <v>196.413481047746</v>
+        <v>196.6350813639692</v>
       </c>
       <c r="E27">
-        <v>38.875</v>
+        <v>41.03</v>
       </c>
       <c r="F27">
-        <v>53.875</v>
+        <v>56.03</v>
       </c>
       <c r="G27">
         <v>23</v>
@@ -3501,28 +3501,28 @@
         <v>13</v>
       </c>
       <c r="M27">
-        <v>3.113975</v>
+        <v>3.238534</v>
       </c>
       <c r="N27">
-        <v>9.886025</v>
+        <v>9.761465999999999</v>
       </c>
       <c r="O27">
-        <v>2.768087</v>
+        <v>2.73321048</v>
       </c>
       <c r="P27">
-        <v>7.117938</v>
+        <v>7.028255519999998</v>
       </c>
       <c r="Q27">
-        <v>57.117938</v>
+        <v>57.02825552</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07758432161683076</v>
+        <v>0.07791685157271741</v>
       </c>
       <c r="T27">
-        <v>0.7340489980792327</v>
+        <v>0.7417286737348132</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.174728441943175</v>
+        <v>4.014161963406899</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06847863016381088</v>
+        <v>0.06904541911499867</v>
       </c>
       <c r="C28">
-        <v>163.6050813639692</v>
+        <v>160.3494971521058</v>
       </c>
       <c r="D28">
-        <v>196.6350813639692</v>
+        <v>195.5344971521058</v>
       </c>
       <c r="E28">
-        <v>41.03</v>
+        <v>43.185</v>
       </c>
       <c r="F28">
-        <v>56.03</v>
+        <v>58.185</v>
       </c>
       <c r="G28">
         <v>23</v>
@@ -3583,45 +3583,45 @@
         <v>13</v>
       </c>
       <c r="M28">
-        <v>3.238534</v>
+        <v>3.5667405</v>
       </c>
       <c r="N28">
-        <v>9.761465999999999</v>
+        <v>9.4332595</v>
       </c>
       <c r="O28">
-        <v>2.73321048</v>
+        <v>2.64131266</v>
       </c>
       <c r="P28">
-        <v>7.028255519999998</v>
+        <v>6.79194684</v>
       </c>
       <c r="Q28">
-        <v>57.02825552</v>
+        <v>56.79194684</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07791685157271741</v>
+        <v>0.07825849193835435</v>
       </c>
       <c r="T28">
-        <v>0.7417286737348132</v>
+        <v>0.7496187514631493</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.014161963406899</v>
+        <v>3.644784362641465</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06904541911499867</v>
+        <v>0.06895700806618649</v>
       </c>
       <c r="C29">
-        <v>160.3494971521058</v>
+        <v>158.3653609933762</v>
       </c>
       <c r="D29">
-        <v>195.5344971521058</v>
+        <v>195.7053609933762</v>
       </c>
       <c r="E29">
-        <v>43.185</v>
+        <v>45.34</v>
       </c>
       <c r="F29">
-        <v>58.185</v>
+        <v>60.34</v>
       </c>
       <c r="G29">
         <v>23</v>
@@ -3665,28 +3665,28 @@
         <v>13</v>
       </c>
       <c r="M29">
-        <v>3.5667405</v>
+        <v>3.698842</v>
       </c>
       <c r="N29">
-        <v>9.4332595</v>
+        <v>9.301157999999999</v>
       </c>
       <c r="O29">
-        <v>2.64131266</v>
+        <v>2.60432424</v>
       </c>
       <c r="P29">
-        <v>6.79194684</v>
+        <v>6.696833759999999</v>
       </c>
       <c r="Q29">
-        <v>56.79194684</v>
+        <v>56.69683376</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07825849193835435</v>
+        <v>0.07860962231414789</v>
       </c>
       <c r="T29">
-        <v>0.7496187514631493</v>
+        <v>0.7577279980172724</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.644784362641465</v>
+        <v>3.514613492547126</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06895700806618649</v>
+        <v>0.06945323701737428</v>
       </c>
       <c r="C30">
-        <v>158.3653609933762</v>
+        <v>155.2551919753639</v>
       </c>
       <c r="D30">
-        <v>195.7053609933762</v>
+        <v>194.7501919753639</v>
       </c>
       <c r="E30">
-        <v>45.34</v>
+        <v>47.495</v>
       </c>
       <c r="F30">
-        <v>60.34</v>
+        <v>62.495</v>
       </c>
       <c r="G30">
         <v>23</v>
@@ -3747,45 +3747,45 @@
         <v>13</v>
       </c>
       <c r="M30">
-        <v>3.698842</v>
+        <v>4.005929500000001</v>
       </c>
       <c r="N30">
-        <v>9.301157999999999</v>
+        <v>8.994070499999999</v>
       </c>
       <c r="O30">
-        <v>2.60432424</v>
+        <v>2.51833974</v>
       </c>
       <c r="P30">
-        <v>6.696833759999999</v>
+        <v>6.475730759999999</v>
       </c>
       <c r="Q30">
-        <v>56.69683376</v>
+        <v>56.47573076</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07860962231414789</v>
+        <v>0.07897064368644266</v>
       </c>
       <c r="T30">
-        <v>0.7577279980172724</v>
+        <v>0.7660656740517935</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.28</v>
       </c>
       <c r="W30">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.514613492547126</v>
+        <v>3.245189412344875</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06945323701737428</v>
+        <v>0.06938498596856207</v>
       </c>
       <c r="C31">
-        <v>155.2551919753639</v>
+        <v>153.2310120106642</v>
       </c>
       <c r="D31">
-        <v>194.7501919753639</v>
+        <v>194.8810120106642</v>
       </c>
       <c r="E31">
-        <v>47.495</v>
+        <v>49.64999999999999</v>
       </c>
       <c r="F31">
-        <v>62.495</v>
+        <v>64.64999999999999</v>
       </c>
       <c r="G31">
         <v>23</v>
@@ -3829,28 +3829,28 @@
         <v>13</v>
       </c>
       <c r="M31">
-        <v>4.0059295</v>
+        <v>4.144064999999999</v>
       </c>
       <c r="N31">
-        <v>8.994070499999999</v>
+        <v>8.855935000000001</v>
       </c>
       <c r="O31">
-        <v>2.51833974</v>
+        <v>2.479661800000001</v>
       </c>
       <c r="P31">
-        <v>6.475730759999999</v>
+        <v>6.3762732</v>
       </c>
       <c r="Q31">
-        <v>56.47573076</v>
+        <v>56.3762732</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07897064368644266</v>
+        <v>0.0793419799550887</v>
       </c>
       <c r="T31">
-        <v>0.7660656740517935</v>
+        <v>0.7746415694015867</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.245189412344875</v>
+        <v>3.13701643193338</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06938498596856207</v>
+        <v>0.06931673491974988</v>
       </c>
       <c r="C32">
-        <v>153.2310120106642</v>
+        <v>151.2070079162435</v>
       </c>
       <c r="D32">
-        <v>194.8810120106642</v>
+        <v>195.0120079162435</v>
       </c>
       <c r="E32">
-        <v>49.64999999999999</v>
+        <v>51.80499999999999</v>
       </c>
       <c r="F32">
-        <v>64.64999999999999</v>
+        <v>66.80499999999999</v>
       </c>
       <c r="G32">
         <v>23</v>
@@ -3911,28 +3911,28 @@
         <v>13</v>
       </c>
       <c r="M32">
-        <v>4.144064999999999</v>
+        <v>4.2822005</v>
       </c>
       <c r="N32">
-        <v>8.855935000000001</v>
+        <v>8.7177995</v>
       </c>
       <c r="O32">
-        <v>2.479661800000001</v>
+        <v>2.44098386</v>
       </c>
       <c r="P32">
-        <v>6.3762732</v>
+        <v>6.27681564</v>
       </c>
       <c r="Q32">
-        <v>56.3762732</v>
+        <v>56.27681564</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0793419799550887</v>
+        <v>0.07972407959384041</v>
       </c>
       <c r="T32">
-        <v>0.7746415694015867</v>
+        <v>0.7834660414281852</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.13701643193338</v>
+        <v>3.035822353483915</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06931673491974988</v>
+        <v>0.07104560387093768</v>
       </c>
       <c r="C33">
-        <v>151.2070079162435</v>
+        <v>145.7871088107395</v>
       </c>
       <c r="D33">
-        <v>195.0120079162435</v>
+        <v>191.7471088107395</v>
       </c>
       <c r="E33">
-        <v>51.80499999999999</v>
+        <v>53.96000000000001</v>
       </c>
       <c r="F33">
-        <v>66.80499999999999</v>
+        <v>68.96000000000001</v>
       </c>
       <c r="G33">
         <v>23</v>
@@ -3993,45 +3993,45 @@
         <v>13</v>
       </c>
       <c r="M33">
-        <v>4.2822005</v>
+        <v>4.958224000000001</v>
       </c>
       <c r="N33">
-        <v>8.7177995</v>
+        <v>8.041775999999999</v>
       </c>
       <c r="O33">
-        <v>2.44098386</v>
+        <v>2.25169728</v>
       </c>
       <c r="P33">
-        <v>6.27681564</v>
+        <v>5.790078719999999</v>
       </c>
       <c r="Q33">
-        <v>56.27681564</v>
+        <v>55.79007872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07972407959384041</v>
+        <v>0.08011741745726131</v>
       </c>
       <c r="T33">
-        <v>0.7834660414281852</v>
+        <v>0.7925500567496839</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.28</v>
       </c>
       <c r="W33">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.035822353483915</v>
+        <v>2.621906553636947</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07104560387093768</v>
+        <v>0.07103351282212549</v>
       </c>
       <c r="C34">
-        <v>145.7871088107395</v>
+        <v>143.6545626178866</v>
       </c>
       <c r="D34">
-        <v>191.7471088107395</v>
+        <v>191.7695626178866</v>
       </c>
       <c r="E34">
-        <v>53.96000000000001</v>
+        <v>56.11500000000001</v>
       </c>
       <c r="F34">
-        <v>68.96000000000001</v>
+        <v>71.11500000000001</v>
       </c>
       <c r="G34">
         <v>23</v>
@@ -4075,28 +4075,28 @@
         <v>13</v>
       </c>
       <c r="M34">
-        <v>4.958224000000001</v>
+        <v>5.113168500000001</v>
       </c>
       <c r="N34">
-        <v>8.041775999999999</v>
+        <v>7.886831499999999</v>
       </c>
       <c r="O34">
-        <v>2.25169728</v>
+        <v>2.20831282</v>
       </c>
       <c r="P34">
-        <v>5.790078719999999</v>
+        <v>5.678518679999999</v>
       </c>
       <c r="Q34">
-        <v>55.79007872</v>
+        <v>55.67851868</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08011741745726131</v>
+        <v>0.08052249674944104</v>
       </c>
       <c r="T34">
-        <v>0.7925500567496839</v>
+        <v>0.8019052367076451</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.621906553636947</v>
+        <v>2.542454839890373</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07103351282212549</v>
+        <v>0.0719761417733133</v>
       </c>
       <c r="C35">
-        <v>143.6545626178866</v>
+        <v>139.7646771030792</v>
       </c>
       <c r="D35">
-        <v>191.7695626178866</v>
+        <v>190.0346771030792</v>
       </c>
       <c r="E35">
-        <v>56.11500000000001</v>
+        <v>58.27000000000001</v>
       </c>
       <c r="F35">
-        <v>71.11500000000001</v>
+        <v>73.27000000000001</v>
       </c>
       <c r="G35">
         <v>23</v>
@@ -4157,45 +4157,45 @@
         <v>13</v>
       </c>
       <c r="M35">
-        <v>5.113168500000001</v>
+        <v>5.553866000000001</v>
       </c>
       <c r="N35">
-        <v>7.886831499999999</v>
+        <v>7.446133999999999</v>
       </c>
       <c r="O35">
-        <v>2.20831282</v>
+        <v>2.08491752</v>
       </c>
       <c r="P35">
-        <v>5.678518679999999</v>
+        <v>5.36121648</v>
       </c>
       <c r="Q35">
-        <v>55.67851868</v>
+        <v>55.36121648</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08052249674944104</v>
+        <v>0.08093985117168681</v>
       </c>
       <c r="T35">
-        <v>0.8019052367076451</v>
+        <v>0.8115439069673629</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.28</v>
       </c>
       <c r="W35">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.542454839890373</v>
+        <v>2.340711857290039</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0719761417733133</v>
+        <v>0.07199213072450109</v>
       </c>
       <c r="C36">
-        <v>139.7646771030792</v>
+        <v>137.5805205241423</v>
       </c>
       <c r="D36">
-        <v>190.0346771030792</v>
+        <v>190.0055205241424</v>
       </c>
       <c r="E36">
-        <v>58.27000000000001</v>
+        <v>60.42500000000001</v>
       </c>
       <c r="F36">
-        <v>73.27000000000001</v>
+        <v>75.42500000000001</v>
       </c>
       <c r="G36">
         <v>23</v>
@@ -4239,28 +4239,28 @@
         <v>13</v>
       </c>
       <c r="M36">
-        <v>5.553866000000001</v>
+        <v>5.717215000000001</v>
       </c>
       <c r="N36">
-        <v>7.446133999999999</v>
+        <v>7.282784999999999</v>
       </c>
       <c r="O36">
-        <v>2.08491752</v>
+        <v>2.0391798</v>
       </c>
       <c r="P36">
-        <v>5.36121648</v>
+        <v>5.243605199999999</v>
       </c>
       <c r="Q36">
-        <v>55.36121648</v>
+        <v>55.2436052</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08093985117168681</v>
+        <v>0.08137004726846322</v>
       </c>
       <c r="T36">
-        <v>0.8115439069673629</v>
+        <v>0.8214791516966103</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.340711857290039</v>
+        <v>2.27383437565318</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07199213072450109</v>
+        <v>0.07200811967568889</v>
       </c>
       <c r="C37">
-        <v>137.5805205241423</v>
+        <v>135.3963728906853</v>
       </c>
       <c r="D37">
-        <v>190.0055205241424</v>
+        <v>189.9763728906853</v>
       </c>
       <c r="E37">
-        <v>60.42500000000001</v>
+        <v>62.58000000000001</v>
       </c>
       <c r="F37">
-        <v>75.42500000000001</v>
+        <v>77.58000000000001</v>
       </c>
       <c r="G37">
         <v>23</v>
@@ -4321,28 +4321,28 @@
         <v>13</v>
       </c>
       <c r="M37">
-        <v>5.717215000000001</v>
+        <v>5.880564000000001</v>
       </c>
       <c r="N37">
-        <v>7.282784999999999</v>
+        <v>7.119435999999999</v>
       </c>
       <c r="O37">
-        <v>2.0391798</v>
+        <v>1.99344208</v>
       </c>
       <c r="P37">
-        <v>5.243605199999999</v>
+        <v>5.125993919999999</v>
       </c>
       <c r="Q37">
-        <v>55.2436052</v>
+        <v>55.12599392</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08137004726846322</v>
+        <v>0.0818136869932639</v>
       </c>
       <c r="T37">
-        <v>0.8214791516966103</v>
+        <v>0.8317248728236467</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.27383437565318</v>
+        <v>2.210672309662814</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07200811967568889</v>
+        <v>0.07202410862687669</v>
       </c>
       <c r="C38">
-        <v>135.3963728906853</v>
+        <v>133.2122341985918</v>
       </c>
       <c r="D38">
-        <v>189.9763728906853</v>
+        <v>189.9472341985918</v>
       </c>
       <c r="E38">
-        <v>62.58</v>
+        <v>64.735</v>
       </c>
       <c r="F38">
-        <v>77.58</v>
+        <v>79.735</v>
       </c>
       <c r="G38">
         <v>23</v>
@@ -4403,28 +4403,28 @@
         <v>13</v>
       </c>
       <c r="M38">
-        <v>5.880564000000001</v>
+        <v>6.043913000000001</v>
       </c>
       <c r="N38">
-        <v>7.119435999999999</v>
+        <v>6.956086999999999</v>
       </c>
       <c r="O38">
-        <v>1.99344208</v>
+        <v>1.94770436</v>
       </c>
       <c r="P38">
-        <v>5.125993919999999</v>
+        <v>5.008382639999999</v>
       </c>
       <c r="Q38">
-        <v>55.12599392</v>
+        <v>55.00838264</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0818136869932639</v>
+        <v>0.0822714105188519</v>
       </c>
       <c r="T38">
-        <v>0.8317248728236467</v>
+        <v>0.8422958549388431</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.210672309662814</v>
+        <v>2.150924409401657</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07202410862687669</v>
+        <v>0.07204009757806451</v>
       </c>
       <c r="C39">
-        <v>133.2122341985918</v>
+        <v>131.0281044437484</v>
       </c>
       <c r="D39">
-        <v>189.9472341985918</v>
+        <v>189.9181044437484</v>
       </c>
       <c r="E39">
-        <v>64.735</v>
+        <v>66.89</v>
       </c>
       <c r="F39">
-        <v>79.735</v>
+        <v>81.89</v>
       </c>
       <c r="G39">
         <v>23</v>
@@ -4485,28 +4485,28 @@
         <v>13</v>
       </c>
       <c r="M39">
-        <v>6.043913000000001</v>
+        <v>6.207262000000001</v>
       </c>
       <c r="N39">
-        <v>6.956086999999999</v>
+        <v>6.792737999999999</v>
       </c>
       <c r="O39">
-        <v>1.94770436</v>
+        <v>1.90196664</v>
       </c>
       <c r="P39">
-        <v>5.008382639999999</v>
+        <v>4.890771359999999</v>
       </c>
       <c r="Q39">
-        <v>55.00838264</v>
+        <v>54.89077136</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0822714105188519</v>
+        <v>0.08274389931945887</v>
       </c>
       <c r="T39">
-        <v>0.8422958549388431</v>
+        <v>0.8532078364771103</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.150924409401657</v>
+        <v>2.094321135470035</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07204009757806451</v>
+        <v>0.0720560865292523</v>
       </c>
       <c r="C40">
-        <v>131.0281044437484</v>
+        <v>128.8439836220438</v>
       </c>
       <c r="D40">
-        <v>189.9181044437484</v>
+        <v>189.8889836220438</v>
       </c>
       <c r="E40">
-        <v>66.89</v>
+        <v>69.045</v>
       </c>
       <c r="F40">
-        <v>81.89</v>
+        <v>84.045</v>
       </c>
       <c r="G40">
         <v>23</v>
@@ -4567,28 +4567,28 @@
         <v>13</v>
       </c>
       <c r="M40">
-        <v>6.207262000000001</v>
+        <v>6.370611</v>
       </c>
       <c r="N40">
-        <v>6.792737999999999</v>
+        <v>6.629389</v>
       </c>
       <c r="O40">
-        <v>1.90196664</v>
+        <v>1.85622892</v>
       </c>
       <c r="P40">
-        <v>4.890771359999999</v>
+        <v>4.773160079999999</v>
       </c>
       <c r="Q40">
-        <v>54.89077136</v>
+        <v>54.77316008</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08274389931945887</v>
+        <v>0.0832318795561513</v>
       </c>
       <c r="T40">
-        <v>0.8532078364771103</v>
+        <v>0.8644775879018779</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.094321135470035</v>
+        <v>2.040620593534906</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0720560865292523</v>
+        <v>0.07616167548044009</v>
       </c>
       <c r="C41">
-        <v>128.8439836220438</v>
+        <v>119.4957973817128</v>
       </c>
       <c r="D41">
-        <v>189.8889836220438</v>
+        <v>182.6957973817128</v>
       </c>
       <c r="E41">
-        <v>69.045</v>
+        <v>71.2</v>
       </c>
       <c r="F41">
-        <v>84.045</v>
+        <v>86.2</v>
       </c>
       <c r="G41">
         <v>23</v>
@@ -4649,45 +4649,45 @@
         <v>13</v>
       </c>
       <c r="M41">
-        <v>6.370611</v>
+        <v>7.758</v>
       </c>
       <c r="N41">
-        <v>6.629389</v>
+        <v>5.242</v>
       </c>
       <c r="O41">
-        <v>1.85622892</v>
+        <v>1.46776</v>
       </c>
       <c r="P41">
-        <v>4.773160079999999</v>
+        <v>3.77424</v>
       </c>
       <c r="Q41">
-        <v>54.77316008</v>
+        <v>53.77424</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0832318795561513</v>
+        <v>0.0837361258007335</v>
       </c>
       <c r="T41">
-        <v>0.8644775879018779</v>
+        <v>0.8761229977074713</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.28</v>
       </c>
       <c r="W41">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.040620593534906</v>
+        <v>1.675689610724413</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07616167548044009</v>
+        <v>0.07627990443162791</v>
       </c>
       <c r="C42">
-        <v>119.4957973817128</v>
+        <v>117.1417186038621</v>
       </c>
       <c r="D42">
-        <v>182.6957973817128</v>
+        <v>182.4967186038621</v>
       </c>
       <c r="E42">
-        <v>71.2</v>
+        <v>73.355</v>
       </c>
       <c r="F42">
-        <v>86.2</v>
+        <v>88.355</v>
       </c>
       <c r="G42">
         <v>23</v>
@@ -4731,28 +4731,28 @@
         <v>13</v>
       </c>
       <c r="M42">
-        <v>7.758</v>
+        <v>7.95195</v>
       </c>
       <c r="N42">
-        <v>5.242</v>
+        <v>5.04805</v>
       </c>
       <c r="O42">
-        <v>1.46776</v>
+        <v>1.413454</v>
       </c>
       <c r="P42">
-        <v>3.77424</v>
+        <v>3.634596</v>
       </c>
       <c r="Q42">
-        <v>53.77424</v>
+        <v>53.634596</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0837361258007335</v>
+        <v>0.08425746513835237</v>
       </c>
       <c r="T42">
-        <v>0.8761229977074713</v>
+        <v>0.8881631671674916</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.675689610724413</v>
+        <v>1.634819132414062</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07627990443162791</v>
+        <v>0.0763981333828157</v>
       </c>
       <c r="C43">
-        <v>117.1417186038621</v>
+        <v>114.788073215515</v>
       </c>
       <c r="D43">
-        <v>182.4967186038621</v>
+        <v>182.298073215515</v>
       </c>
       <c r="E43">
-        <v>73.355</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F43">
-        <v>88.355</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="G43">
         <v>23</v>
@@ -4813,28 +4813,28 @@
         <v>13</v>
       </c>
       <c r="M43">
-        <v>7.95195</v>
+        <v>8.145900000000001</v>
       </c>
       <c r="N43">
-        <v>5.04805</v>
+        <v>4.854099999999999</v>
       </c>
       <c r="O43">
-        <v>1.413454</v>
+        <v>1.359148</v>
       </c>
       <c r="P43">
-        <v>3.634596</v>
+        <v>3.494951999999999</v>
       </c>
       <c r="Q43">
-        <v>53.634596</v>
+        <v>53.494952</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08425746513835237</v>
+        <v>0.08479678169450983</v>
       </c>
       <c r="T43">
-        <v>0.8881631671674916</v>
+        <v>0.9006185148847539</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.634819132414062</v>
+        <v>1.595894867356584</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0763981333828157</v>
+        <v>0.07651636233400351</v>
       </c>
       <c r="C44">
-        <v>114.788073215515</v>
+        <v>112.4348598029931</v>
       </c>
       <c r="D44">
-        <v>182.298073215515</v>
+        <v>182.0998598029931</v>
       </c>
       <c r="E44">
-        <v>75.50999999999999</v>
+        <v>77.66499999999999</v>
       </c>
       <c r="F44">
-        <v>90.50999999999999</v>
+        <v>92.66499999999999</v>
       </c>
       <c r="G44">
         <v>23</v>
@@ -4895,28 +4895,28 @@
         <v>13</v>
       </c>
       <c r="M44">
-        <v>8.145899999999999</v>
+        <v>8.339849999999998</v>
       </c>
       <c r="N44">
-        <v>4.854100000000001</v>
+        <v>4.660150000000002</v>
       </c>
       <c r="O44">
-        <v>1.359148</v>
+        <v>1.304842000000001</v>
       </c>
       <c r="P44">
-        <v>3.494952000000001</v>
+        <v>3.355308000000001</v>
       </c>
       <c r="Q44">
-        <v>53.494952</v>
+        <v>53.355308</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08479678169450983</v>
+        <v>0.08535502163860265</v>
       </c>
       <c r="T44">
-        <v>0.9006185148847539</v>
+        <v>0.9135108923464814</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.595894867356584</v>
+        <v>1.558781033232013</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07651636233400351</v>
+        <v>0.0766345912851913</v>
       </c>
       <c r="C45">
-        <v>112.4348598029931</v>
+        <v>110.0820769587599</v>
       </c>
       <c r="D45">
-        <v>182.0998598029931</v>
+        <v>181.9020769587599</v>
       </c>
       <c r="E45">
-        <v>77.66499999999999</v>
+        <v>79.82000000000001</v>
       </c>
       <c r="F45">
-        <v>92.66499999999999</v>
+        <v>94.82000000000001</v>
       </c>
       <c r="G45">
         <v>23</v>
@@ -4977,28 +4977,28 @@
         <v>13</v>
       </c>
       <c r="M45">
-        <v>8.339849999999998</v>
+        <v>8.533800000000001</v>
       </c>
       <c r="N45">
-        <v>4.660150000000002</v>
+        <v>4.466199999999999</v>
       </c>
       <c r="O45">
-        <v>1.304842000000001</v>
+        <v>1.250536</v>
       </c>
       <c r="P45">
-        <v>3.355308000000001</v>
+        <v>3.215663999999999</v>
       </c>
       <c r="Q45">
-        <v>53.355308</v>
+        <v>53.215664</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08535502163860265</v>
+        <v>0.0859331987235559</v>
       </c>
       <c r="T45">
-        <v>0.9135108923464814</v>
+        <v>0.9268637118604137</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.558781033232013</v>
+        <v>1.523354191567648</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0766345912851913</v>
+        <v>0.09704226368377811</v>
       </c>
       <c r="C46">
-        <v>110.0820769587599</v>
+        <v>79.20862721251346</v>
       </c>
       <c r="D46">
-        <v>181.9020769587599</v>
+        <v>153.1836272125135</v>
       </c>
       <c r="E46">
-        <v>79.82000000000001</v>
+        <v>81.97500000000001</v>
       </c>
       <c r="F46">
-        <v>94.82000000000001</v>
+        <v>96.97500000000001</v>
       </c>
       <c r="G46">
         <v>23</v>
@@ -5059,45 +5059,45 @@
         <v>13</v>
       </c>
       <c r="M46">
-        <v>8.533800000000001</v>
+        <v>14.23593</v>
       </c>
       <c r="N46">
-        <v>4.466199999999999</v>
+        <v>-1.235930000000003</v>
       </c>
       <c r="O46">
-        <v>1.250536</v>
+        <v>-0.3460604000000009</v>
       </c>
       <c r="P46">
-        <v>3.215663999999999</v>
+        <v>-0.8898696000000024</v>
       </c>
       <c r="Q46">
-        <v>53.215664</v>
+        <v>49.1101304</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0859331987235559</v>
+        <v>0.08704220901796397</v>
       </c>
       <c r="T46">
-        <v>0.9268637118604137</v>
+        <v>0.9524759588444337</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.28</v>
+        <v>0.2556910577672129</v>
       </c>
       <c r="W46">
-        <v>0.0648</v>
+        <v>0.1092645527197732</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.523354191567648</v>
+        <v>0.9131823491686175</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09704226368377811</v>
+        <v>0.09805226368377812</v>
       </c>
       <c r="C47">
-        <v>79.20862721251346</v>
+        <v>75.86599117258073</v>
       </c>
       <c r="D47">
-        <v>153.1836272125135</v>
+        <v>151.9959911725807</v>
       </c>
       <c r="E47">
-        <v>81.97500000000001</v>
+        <v>84.13000000000001</v>
       </c>
       <c r="F47">
-        <v>96.97500000000001</v>
+        <v>99.13000000000001</v>
       </c>
       <c r="G47">
         <v>23</v>
@@ -5141,37 +5141,37 @@
         <v>13</v>
       </c>
       <c r="M47">
-        <v>14.23593</v>
+        <v>14.552284</v>
       </c>
       <c r="N47">
-        <v>-1.235930000000003</v>
+        <v>-1.552284000000002</v>
       </c>
       <c r="O47">
-        <v>-0.3460604000000009</v>
+        <v>-0.4346395200000006</v>
       </c>
       <c r="P47">
-        <v>-0.8898696000000024</v>
+        <v>-1.117644480000001</v>
       </c>
       <c r="Q47">
-        <v>49.1101304</v>
+        <v>48.88235552</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08704220901796397</v>
+        <v>0.08780595362940775</v>
       </c>
       <c r="T47">
-        <v>0.9524759588444337</v>
+        <v>0.9701144025267382</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2556910577672129</v>
+        <v>0.250132556511404</v>
       </c>
       <c r="W47">
-        <v>0.1092645527197732</v>
+        <v>0.1100805407041259</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9131823491686175</v>
+        <v>0.8933305589692998</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09805226368377812</v>
+        <v>0.09906226368377813</v>
       </c>
       <c r="C48">
-        <v>75.86599117258073</v>
+        <v>72.54162899183173</v>
       </c>
       <c r="D48">
-        <v>151.9959911725807</v>
+        <v>150.8266289918317</v>
       </c>
       <c r="E48">
-        <v>84.13000000000001</v>
+        <v>86.28500000000001</v>
       </c>
       <c r="F48">
-        <v>99.13000000000001</v>
+        <v>101.285</v>
       </c>
       <c r="G48">
         <v>23</v>
@@ -5223,37 +5223,37 @@
         <v>13</v>
       </c>
       <c r="M48">
-        <v>14.552284</v>
+        <v>14.868638</v>
       </c>
       <c r="N48">
-        <v>-1.552284000000002</v>
+        <v>-1.868638000000002</v>
       </c>
       <c r="O48">
-        <v>-0.4346395200000006</v>
+        <v>-0.5232186400000007</v>
       </c>
       <c r="P48">
-        <v>-1.117644480000001</v>
+        <v>-1.345419360000002</v>
       </c>
       <c r="Q48">
-        <v>48.88235552</v>
+        <v>48.65458064</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08780595362940775</v>
+        <v>0.08859851879222677</v>
       </c>
       <c r="T48">
-        <v>0.9701144025267382</v>
+        <v>0.9884184478574314</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.250132556511404</v>
+        <v>0.2448105872239273</v>
       </c>
       <c r="W48">
-        <v>0.1100805407041259</v>
+        <v>0.1108618057955275</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8933305589692998</v>
+        <v>0.8743235257997402</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09906226368377813</v>
+        <v>0.1000722636837781</v>
       </c>
       <c r="C49">
-        <v>72.54162899183173</v>
+        <v>69.23512212731232</v>
       </c>
       <c r="D49">
-        <v>150.8266289918317</v>
+        <v>149.6751221273123</v>
       </c>
       <c r="E49">
-        <v>86.28500000000001</v>
+        <v>88.44000000000001</v>
       </c>
       <c r="F49">
-        <v>101.285</v>
+        <v>103.44</v>
       </c>
       <c r="G49">
         <v>23</v>
@@ -5305,37 +5305,37 @@
         <v>13</v>
       </c>
       <c r="M49">
-        <v>14.868638</v>
+        <v>15.184992</v>
       </c>
       <c r="N49">
-        <v>-1.868638000000002</v>
+        <v>-2.184992000000003</v>
       </c>
       <c r="O49">
-        <v>-0.5232186400000007</v>
+        <v>-0.6117977600000009</v>
       </c>
       <c r="P49">
-        <v>-1.345419360000002</v>
+        <v>-1.573194240000002</v>
       </c>
       <c r="Q49">
-        <v>48.65458064</v>
+        <v>48.42680576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08859851879222677</v>
+        <v>0.08942156723053882</v>
       </c>
       <c r="T49">
-        <v>0.9884184478574314</v>
+        <v>1.007426494931613</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2448105872239273</v>
+        <v>0.2397103666567621</v>
       </c>
       <c r="W49">
-        <v>0.1108618057955275</v>
+        <v>0.1116105181747873</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8743235257997402</v>
+        <v>0.856108452345579</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1000722636837781</v>
+        <v>0.1010822636837781</v>
       </c>
       <c r="C50">
-        <v>69.23512212731234</v>
+        <v>65.94606472092138</v>
       </c>
       <c r="D50">
-        <v>149.6751221273123</v>
+        <v>148.5410647209214</v>
       </c>
       <c r="E50">
-        <v>88.44</v>
+        <v>90.595</v>
       </c>
       <c r="F50">
-        <v>103.44</v>
+        <v>105.595</v>
       </c>
       <c r="G50">
         <v>23</v>
@@ -5387,37 +5387,37 @@
         <v>13</v>
       </c>
       <c r="M50">
-        <v>15.184992</v>
+        <v>15.501346</v>
       </c>
       <c r="N50">
-        <v>-2.184992000000001</v>
+        <v>-2.501346000000002</v>
       </c>
       <c r="O50">
-        <v>-0.6117977600000004</v>
+        <v>-0.7003768800000005</v>
       </c>
       <c r="P50">
-        <v>-1.573194240000001</v>
+        <v>-1.800969120000001</v>
       </c>
       <c r="Q50">
-        <v>48.42680576</v>
+        <v>48.19903088</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08942156723053882</v>
+        <v>0.09027689207819645</v>
       </c>
       <c r="T50">
-        <v>1.007426494931613</v>
+        <v>1.027179955616546</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2397103666567622</v>
+        <v>0.2348183183576446</v>
       </c>
       <c r="W50">
-        <v>0.1116105181747873</v>
+        <v>0.1123286708650978</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8561084523455791</v>
+        <v>0.8386368512773019</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1010822636837781</v>
+        <v>0.1020922636837781</v>
       </c>
       <c r="C51">
-        <v>65.94606472092138</v>
+        <v>62.67406312247221</v>
       </c>
       <c r="D51">
-        <v>148.5410647209214</v>
+        <v>147.4240631224722</v>
       </c>
       <c r="E51">
-        <v>90.595</v>
+        <v>92.75</v>
       </c>
       <c r="F51">
-        <v>105.595</v>
+        <v>107.75</v>
       </c>
       <c r="G51">
         <v>23</v>
@@ -5469,37 +5469,37 @@
         <v>13</v>
       </c>
       <c r="M51">
-        <v>15.501346</v>
+        <v>15.8177</v>
       </c>
       <c r="N51">
-        <v>-2.501346000000002</v>
+        <v>-2.817700000000002</v>
       </c>
       <c r="O51">
-        <v>-0.7003768800000005</v>
+        <v>-0.7889560000000007</v>
       </c>
       <c r="P51">
-        <v>-1.800969120000001</v>
+        <v>-2.028744000000001</v>
       </c>
       <c r="Q51">
-        <v>48.19903088</v>
+        <v>47.971256</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09027689207819645</v>
+        <v>0.09116642991976037</v>
       </c>
       <c r="T51">
-        <v>1.027179955616546</v>
+        <v>1.047723554728877</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2348183183576446</v>
+        <v>0.2301219519904917</v>
       </c>
       <c r="W51">
-        <v>0.1123286708650978</v>
+        <v>0.1130180974477958</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8386368512773019</v>
+        <v>0.8218641142517559</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1020922636837781</v>
+        <v>0.1031022636837781</v>
       </c>
       <c r="C52">
-        <v>62.67406312247221</v>
+        <v>59.41873543411182</v>
       </c>
       <c r="D52">
-        <v>147.4240631224722</v>
+        <v>146.3237354341118</v>
       </c>
       <c r="E52">
-        <v>92.75</v>
+        <v>94.905</v>
       </c>
       <c r="F52">
-        <v>107.75</v>
+        <v>109.905</v>
       </c>
       <c r="G52">
         <v>23</v>
@@ -5551,37 +5551,37 @@
         <v>13</v>
       </c>
       <c r="M52">
-        <v>15.8177</v>
+        <v>16.134054</v>
       </c>
       <c r="N52">
-        <v>-2.817700000000002</v>
+        <v>-3.134054000000003</v>
       </c>
       <c r="O52">
-        <v>-0.7889560000000007</v>
+        <v>-0.8775351200000008</v>
       </c>
       <c r="P52">
-        <v>-2.028744000000001</v>
+        <v>-2.256518880000002</v>
       </c>
       <c r="Q52">
-        <v>47.971256</v>
+        <v>47.74348112</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09116642991976037</v>
+        <v>0.09209227542832692</v>
       </c>
       <c r="T52">
-        <v>1.047723554728877</v>
+        <v>1.069105668090691</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2301219519904917</v>
+        <v>0.2256097568534232</v>
       </c>
       <c r="W52">
-        <v>0.1130180974477958</v>
+        <v>0.1136804876939175</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8218641142517559</v>
+        <v>0.8057491316193685</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1031022636837781</v>
+        <v>0.1329854027950559</v>
       </c>
       <c r="C53">
-        <v>59.41873543411182</v>
+        <v>30.79592498696223</v>
       </c>
       <c r="D53">
-        <v>146.3237354341118</v>
+        <v>119.8559249869622</v>
       </c>
       <c r="E53">
-        <v>94.905</v>
+        <v>97.06</v>
       </c>
       <c r="F53">
-        <v>109.905</v>
+        <v>112.06</v>
       </c>
       <c r="G53">
         <v>23</v>
@@ -5633,45 +5633,45 @@
         <v>13</v>
       </c>
       <c r="M53">
-        <v>16.134054</v>
+        <v>22.501648</v>
       </c>
       <c r="N53">
-        <v>-3.134054000000003</v>
+        <v>-9.501647999999999</v>
       </c>
       <c r="O53">
-        <v>-0.8775351200000008</v>
+        <v>-2.66046144</v>
       </c>
       <c r="P53">
-        <v>-2.256518880000002</v>
+        <v>-6.841186559999999</v>
       </c>
       <c r="Q53">
-        <v>47.74348112</v>
+        <v>43.15881344</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09209227542832692</v>
+        <v>0.09470907098157916</v>
       </c>
       <c r="T53">
-        <v>1.069105668090691</v>
+        <v>1.129539745533006</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2256097568534232</v>
+        <v>0.1617659293221546</v>
       </c>
       <c r="W53">
-        <v>0.1136804876939175</v>
+        <v>0.1683174013921114</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8057491316193685</v>
+        <v>0.5777354618648376</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1329854027950559</v>
+        <v>0.1345354027950559</v>
       </c>
       <c r="C54">
-        <v>30.79592498696223</v>
+        <v>27.52685481554741</v>
       </c>
       <c r="D54">
-        <v>119.8559249869622</v>
+        <v>118.7418548155474</v>
       </c>
       <c r="E54">
-        <v>97.06</v>
+        <v>99.215</v>
       </c>
       <c r="F54">
-        <v>112.06</v>
+        <v>114.215</v>
       </c>
       <c r="G54">
         <v>23</v>
@@ -5715,37 +5715,37 @@
         <v>13</v>
       </c>
       <c r="M54">
-        <v>22.501648</v>
+        <v>22.934372</v>
       </c>
       <c r="N54">
-        <v>-9.501647999999999</v>
+        <v>-9.934372</v>
       </c>
       <c r="O54">
-        <v>-2.66046144</v>
+        <v>-2.78162416</v>
       </c>
       <c r="P54">
-        <v>-6.841186559999999</v>
+        <v>-7.15274784</v>
       </c>
       <c r="Q54">
-        <v>43.15881344</v>
+        <v>42.84725216</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09470907098157916</v>
+        <v>0.09574968951310212</v>
       </c>
       <c r="T54">
-        <v>1.129539745533006</v>
+        <v>1.153572506076262</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1617659293221546</v>
+        <v>0.1587137419764535</v>
       </c>
       <c r="W54">
-        <v>0.1683174013921114</v>
+        <v>0.1689302806111281</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5777354618648376</v>
+        <v>0.5668347927730483</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1345354027950559</v>
+        <v>0.1360854027950559</v>
       </c>
       <c r="C55">
-        <v>27.52685481554741</v>
+        <v>24.2783046473815</v>
       </c>
       <c r="D55">
-        <v>118.7418548155474</v>
+        <v>117.6483046473815</v>
       </c>
       <c r="E55">
-        <v>99.215</v>
+        <v>101.37</v>
       </c>
       <c r="F55">
-        <v>114.215</v>
+        <v>116.37</v>
       </c>
       <c r="G55">
         <v>23</v>
@@ -5797,37 +5797,37 @@
         <v>13</v>
       </c>
       <c r="M55">
-        <v>22.934372</v>
+        <v>23.367096</v>
       </c>
       <c r="N55">
-        <v>-9.934372</v>
+        <v>-10.367096</v>
       </c>
       <c r="O55">
-        <v>-2.78162416</v>
+        <v>-2.90278688</v>
       </c>
       <c r="P55">
-        <v>-7.15274784</v>
+        <v>-7.464309119999999</v>
       </c>
       <c r="Q55">
-        <v>42.84725216</v>
+        <v>42.53569088</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09574968951310212</v>
+        <v>0.09683555232860433</v>
       </c>
       <c r="T55">
-        <v>1.153572506076262</v>
+        <v>1.178650169251833</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1587137419764535</v>
+        <v>0.1557745986065192</v>
       </c>
       <c r="W55">
-        <v>0.1689302806111281</v>
+        <v>0.1695204605998109</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5668347927730483</v>
+        <v>0.55633785216614</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1360854027950559</v>
+        <v>0.1376354027950559</v>
       </c>
       <c r="C56">
-        <v>24.2783046473815</v>
+        <v>21.0497127206128</v>
       </c>
       <c r="D56">
-        <v>117.6483046473815</v>
+        <v>116.5747127206128</v>
       </c>
       <c r="E56">
-        <v>101.37</v>
+        <v>103.525</v>
       </c>
       <c r="F56">
-        <v>116.37</v>
+        <v>118.525</v>
       </c>
       <c r="G56">
         <v>23</v>
@@ -5879,37 +5879,37 @@
         <v>13</v>
       </c>
       <c r="M56">
-        <v>23.367096</v>
+        <v>23.79982</v>
       </c>
       <c r="N56">
-        <v>-10.367096</v>
+        <v>-10.79982</v>
       </c>
       <c r="O56">
-        <v>-2.90278688</v>
+        <v>-3.0239496</v>
       </c>
       <c r="P56">
-        <v>-7.464309119999999</v>
+        <v>-7.775870400000001</v>
       </c>
       <c r="Q56">
-        <v>42.53569088</v>
+        <v>42.2241296</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09683555232860433</v>
+        <v>0.09796967571368445</v>
       </c>
       <c r="T56">
-        <v>1.178650169251833</v>
+        <v>1.204842395235207</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1557745986065192</v>
+        <v>0.1529423331773097</v>
       </c>
       <c r="W56">
-        <v>0.1695204605998109</v>
+        <v>0.1700891794979962</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.55633785216614</v>
+        <v>0.546222618490392</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1376354027950559</v>
+        <v>0.1391854027950559</v>
       </c>
       <c r="C57">
-        <v>21.0497127206128</v>
+        <v>17.84053759324641</v>
       </c>
       <c r="D57">
-        <v>116.5747127206128</v>
+        <v>115.5205375932464</v>
       </c>
       <c r="E57">
-        <v>103.525</v>
+        <v>105.68</v>
       </c>
       <c r="F57">
-        <v>118.525</v>
+        <v>120.68</v>
       </c>
       <c r="G57">
         <v>23</v>
@@ -5961,37 +5961,37 @@
         <v>13</v>
       </c>
       <c r="M57">
-        <v>23.79982</v>
+        <v>24.232544</v>
       </c>
       <c r="N57">
-        <v>-10.79982</v>
+        <v>-11.232544</v>
       </c>
       <c r="O57">
-        <v>-3.0239496</v>
+        <v>-3.14511232</v>
       </c>
       <c r="P57">
-        <v>-7.775870400000001</v>
+        <v>-8.08743168</v>
       </c>
       <c r="Q57">
-        <v>42.2241296</v>
+        <v>41.91256832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09796967571368445</v>
+        <v>0.09915535016172272</v>
       </c>
       <c r="T57">
-        <v>1.204842395235207</v>
+        <v>1.232225176945098</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1529423331773097</v>
+        <v>0.1502112200848578</v>
       </c>
       <c r="W57">
-        <v>0.1700891794979962</v>
+        <v>0.1706375870069606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.546222618490392</v>
+        <v>0.5364686431602064</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1391854027950559</v>
+        <v>0.1407354027950559</v>
       </c>
       <c r="C58">
-        <v>17.84053759324641</v>
+        <v>14.65025723262465</v>
       </c>
       <c r="D58">
-        <v>115.5205375932464</v>
+        <v>114.4852572326247</v>
       </c>
       <c r="E58">
-        <v>105.68</v>
+        <v>107.835</v>
       </c>
       <c r="F58">
-        <v>120.68</v>
+        <v>122.835</v>
       </c>
       <c r="G58">
         <v>23</v>
@@ -6043,37 +6043,37 @@
         <v>13</v>
       </c>
       <c r="M58">
-        <v>24.232544</v>
+        <v>24.665268</v>
       </c>
       <c r="N58">
-        <v>-11.232544</v>
+        <v>-11.665268</v>
       </c>
       <c r="O58">
-        <v>-3.14511232</v>
+        <v>-3.26627504</v>
       </c>
       <c r="P58">
-        <v>-8.08743168</v>
+        <v>-8.398992960000001</v>
       </c>
       <c r="Q58">
-        <v>41.91256832</v>
+        <v>41.60100704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09915535016172272</v>
+        <v>0.100396172258507</v>
       </c>
       <c r="T58">
-        <v>1.232225176945098</v>
+        <v>1.260881576408937</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1502112200848578</v>
+        <v>0.1475759355219655</v>
       </c>
       <c r="W58">
-        <v>0.1706375870069606</v>
+        <v>0.1711667521471893</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5364686431602064</v>
+        <v>0.5270569125784483</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1407354027950559</v>
+        <v>0.1422854027950559</v>
       </c>
       <c r="C59">
-        <v>14.65025723262465</v>
+        <v>11.47836815343192</v>
       </c>
       <c r="D59">
-        <v>114.4852572326247</v>
+        <v>113.4683681534319</v>
       </c>
       <c r="E59">
-        <v>107.835</v>
+        <v>109.99</v>
       </c>
       <c r="F59">
-        <v>122.835</v>
+        <v>124.99</v>
       </c>
       <c r="G59">
         <v>23</v>
@@ -6125,37 +6125,37 @@
         <v>13</v>
       </c>
       <c r="M59">
-        <v>24.665268</v>
+        <v>25.097992</v>
       </c>
       <c r="N59">
-        <v>-11.665268</v>
+        <v>-12.097992</v>
       </c>
       <c r="O59">
-        <v>-3.26627504</v>
+        <v>-3.387437760000001</v>
       </c>
       <c r="P59">
-        <v>-8.398992960000001</v>
+        <v>-8.71055424</v>
       </c>
       <c r="Q59">
-        <v>41.60100704</v>
+        <v>41.28944576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.100396172258507</v>
+        <v>0.1016960811218048</v>
       </c>
       <c r="T59">
-        <v>1.260881576408937</v>
+        <v>1.290902566323436</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1475759355219655</v>
+        <v>0.1450315228405523</v>
       </c>
       <c r="W59">
-        <v>0.1711667521471893</v>
+        <v>0.1716776702136171</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5270569125784483</v>
+        <v>0.5179697244305441</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1422854027950559</v>
+        <v>0.1438354027950559</v>
       </c>
       <c r="C60">
-        <v>11.47836815343193</v>
+        <v>8.324384601234144</v>
       </c>
       <c r="D60">
-        <v>113.4683681534319</v>
+        <v>112.4693846012341</v>
       </c>
       <c r="E60">
-        <v>109.99</v>
+        <v>112.145</v>
       </c>
       <c r="F60">
-        <v>124.99</v>
+        <v>127.145</v>
       </c>
       <c r="G60">
         <v>23</v>
@@ -6207,37 +6207,37 @@
         <v>13</v>
       </c>
       <c r="M60">
-        <v>25.097992</v>
+        <v>25.530716</v>
       </c>
       <c r="N60">
-        <v>-12.097992</v>
+        <v>-12.530716</v>
       </c>
       <c r="O60">
-        <v>-3.387437760000001</v>
+        <v>-3.508600480000001</v>
       </c>
       <c r="P60">
-        <v>-8.71055424</v>
+        <v>-9.02211552</v>
       </c>
       <c r="Q60">
-        <v>41.28944576</v>
+        <v>40.97788448</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1016960811218048</v>
+        <v>0.1030594001735561</v>
       </c>
       <c r="T60">
-        <v>1.290902566323436</v>
+        <v>1.322387994770349</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1450315228405523</v>
+        <v>0.1425733614364752</v>
       </c>
       <c r="W60">
-        <v>0.1716776702136171</v>
+        <v>0.1721712690235558</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5179697244305441</v>
+        <v>0.5091905765588399</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1438354027950559</v>
+        <v>0.1453854027950559</v>
       </c>
       <c r="C61">
-        <v>8.324384601234144</v>
+        <v>5.187837778770955</v>
       </c>
       <c r="D61">
-        <v>112.4693846012341</v>
+        <v>111.4878377787709</v>
       </c>
       <c r="E61">
-        <v>112.145</v>
+        <v>114.3</v>
       </c>
       <c r="F61">
-        <v>127.145</v>
+        <v>129.3</v>
       </c>
       <c r="G61">
         <v>23</v>
@@ -6289,37 +6289,37 @@
         <v>13</v>
       </c>
       <c r="M61">
-        <v>25.530716</v>
+        <v>25.96344</v>
       </c>
       <c r="N61">
-        <v>-12.530716</v>
+        <v>-12.96344</v>
       </c>
       <c r="O61">
-        <v>-3.508600480000001</v>
+        <v>-3.6297632</v>
       </c>
       <c r="P61">
-        <v>-9.02211552</v>
+        <v>-9.333676799999999</v>
       </c>
       <c r="Q61">
-        <v>40.97788448</v>
+        <v>40.6663232</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1030594001735561</v>
+        <v>0.104490885177895</v>
       </c>
       <c r="T61">
-        <v>1.322387994770349</v>
+        <v>1.355447694639607</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1425733614364752</v>
+        <v>0.1401971387458673</v>
       </c>
       <c r="W61">
-        <v>0.1721712690235558</v>
+        <v>0.1726484145398298</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5091905765588399</v>
+        <v>0.500704066949526</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1453854027950559</v>
+        <v>0.1686054440065146</v>
       </c>
       <c r="C62">
-        <v>5.187837778770955</v>
+        <v>-9.857751895637904</v>
       </c>
       <c r="D62">
-        <v>111.4878377787709</v>
+        <v>98.59724810436208</v>
       </c>
       <c r="E62">
-        <v>114.3</v>
+        <v>116.455</v>
       </c>
       <c r="F62">
-        <v>129.3</v>
+        <v>131.455</v>
       </c>
       <c r="G62">
         <v>23</v>
@@ -6371,45 +6371,45 @@
         <v>13</v>
       </c>
       <c r="M62">
-        <v>25.96344</v>
+        <v>30.997089</v>
       </c>
       <c r="N62">
-        <v>-12.96344</v>
+        <v>-17.997089</v>
       </c>
       <c r="O62">
-        <v>-3.6297632</v>
+        <v>-5.03918492</v>
       </c>
       <c r="P62">
-        <v>-9.333676799999999</v>
+        <v>-12.95790408</v>
       </c>
       <c r="Q62">
-        <v>40.6663232</v>
+        <v>37.04209592</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.104490885177895</v>
+        <v>0.1068163981605555</v>
       </c>
       <c r="T62">
-        <v>1.355447694639607</v>
+        <v>1.409154691929689</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1401971387458673</v>
+        <v>0.1174303819303806</v>
       </c>
       <c r="W62">
-        <v>0.1726484145398298</v>
+        <v>0.2081099159408163</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.500704066949526</v>
+        <v>0.4193942211799309</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1686054440065146</v>
+        <v>0.1705054440065145</v>
       </c>
       <c r="C63">
-        <v>-9.857751895637904</v>
+        <v>-12.93683528971043</v>
       </c>
       <c r="D63">
-        <v>98.59724810436208</v>
+        <v>97.67316471028956</v>
       </c>
       <c r="E63">
-        <v>116.455</v>
+        <v>118.61</v>
       </c>
       <c r="F63">
-        <v>131.455</v>
+        <v>133.61</v>
       </c>
       <c r="G63">
         <v>23</v>
@@ -6453,37 +6453,37 @@
         <v>13</v>
       </c>
       <c r="M63">
-        <v>30.997089</v>
+        <v>31.505238</v>
       </c>
       <c r="N63">
-        <v>-17.997089</v>
+        <v>-18.505238</v>
       </c>
       <c r="O63">
-        <v>-5.03918492</v>
+        <v>-5.18146664</v>
       </c>
       <c r="P63">
-        <v>-12.95790408</v>
+        <v>-13.32377136</v>
       </c>
       <c r="Q63">
-        <v>37.04209592</v>
+        <v>36.67622864000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1068163981605555</v>
+        <v>0.1084220928489912</v>
       </c>
       <c r="T63">
-        <v>1.409154691929689</v>
+        <v>1.446237710138365</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1174303819303806</v>
+        <v>0.1155363435121487</v>
       </c>
       <c r="W63">
-        <v>0.2081099159408163</v>
+        <v>0.2085565301998353</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4193942211799309</v>
+        <v>0.4126297982576739</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1705054440065145</v>
+        <v>0.1724054440065146</v>
       </c>
       <c r="C64">
-        <v>-12.93683528971043</v>
+        <v>-15.99875793831585</v>
       </c>
       <c r="D64">
-        <v>97.67316471028956</v>
+        <v>96.76624206168417</v>
       </c>
       <c r="E64">
-        <v>118.61</v>
+        <v>120.765</v>
       </c>
       <c r="F64">
-        <v>133.61</v>
+        <v>135.765</v>
       </c>
       <c r="G64">
         <v>23</v>
@@ -6535,37 +6535,37 @@
         <v>13</v>
       </c>
       <c r="M64">
-        <v>31.505238</v>
+        <v>32.013387</v>
       </c>
       <c r="N64">
-        <v>-18.505238</v>
+        <v>-19.013387</v>
       </c>
       <c r="O64">
-        <v>-5.18146664</v>
+        <v>-5.323748360000001</v>
       </c>
       <c r="P64">
-        <v>-13.32377136</v>
+        <v>-13.68963864</v>
       </c>
       <c r="Q64">
-        <v>36.67622864000001</v>
+        <v>36.31036136</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1084220928489912</v>
+        <v>0.1101145818449099</v>
       </c>
       <c r="T64">
-        <v>1.446237710138365</v>
+        <v>1.48532521581778</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1155363435121487</v>
+        <v>0.1137024332976701</v>
       </c>
       <c r="W64">
-        <v>0.2085565301998353</v>
+        <v>0.2089889662284094</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4126297982576739</v>
+        <v>0.4060801189202504</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1724054440065146</v>
+        <v>0.1743054440065146</v>
       </c>
       <c r="C65">
-        <v>-15.99875793831585</v>
+        <v>-19.04399347063655</v>
       </c>
       <c r="D65">
-        <v>96.76624206168417</v>
+        <v>95.87600652936347</v>
       </c>
       <c r="E65">
-        <v>120.765</v>
+        <v>122.92</v>
       </c>
       <c r="F65">
-        <v>135.765</v>
+        <v>137.92</v>
       </c>
       <c r="G65">
         <v>23</v>
@@ -6617,37 +6617,37 @@
         <v>13</v>
       </c>
       <c r="M65">
-        <v>32.013387</v>
+        <v>32.521536</v>
       </c>
       <c r="N65">
-        <v>-19.013387</v>
+        <v>-19.521536</v>
       </c>
       <c r="O65">
-        <v>-5.323748360000001</v>
+        <v>-5.466030080000002</v>
       </c>
       <c r="P65">
-        <v>-13.68963864</v>
+        <v>-14.05550592</v>
       </c>
       <c r="Q65">
-        <v>36.31036136</v>
+        <v>35.94449408</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1101145818449099</v>
+        <v>0.1119010980072685</v>
       </c>
       <c r="T65">
-        <v>1.48532521581778</v>
+        <v>1.526584249590496</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1137024332976701</v>
+        <v>0.111925832777394</v>
       </c>
       <c r="W65">
-        <v>0.2089889662284094</v>
+        <v>0.2094078886310905</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4060801189202504</v>
+        <v>0.3997351170621215</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1743054440065146</v>
+        <v>0.1762054440065146</v>
       </c>
       <c r="C66">
-        <v>-19.04399347063655</v>
+        <v>-22.07299824545848</v>
       </c>
       <c r="D66">
-        <v>95.87600652936347</v>
+        <v>95.00200175454154</v>
       </c>
       <c r="E66">
-        <v>122.92</v>
+        <v>125.075</v>
       </c>
       <c r="F66">
-        <v>137.92</v>
+        <v>140.075</v>
       </c>
       <c r="G66">
         <v>23</v>
@@ -6699,37 +6699,37 @@
         <v>13</v>
       </c>
       <c r="M66">
-        <v>32.521536</v>
+        <v>33.02968500000001</v>
       </c>
       <c r="N66">
-        <v>-19.521536</v>
+        <v>-20.02968500000001</v>
       </c>
       <c r="O66">
-        <v>-5.466030080000002</v>
+        <v>-5.608311800000003</v>
       </c>
       <c r="P66">
-        <v>-14.05550592</v>
+        <v>-14.4213732</v>
       </c>
       <c r="Q66">
-        <v>35.94449408</v>
+        <v>35.5786268</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1119010980072685</v>
+        <v>0.1137897008074762</v>
       </c>
       <c r="T66">
-        <v>1.526584249590496</v>
+        <v>1.570200942435939</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.111925832777394</v>
+        <v>0.110203896888511</v>
       </c>
       <c r="W66">
-        <v>0.2094078886310905</v>
+        <v>0.2098139211136891</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3997351170621215</v>
+        <v>0.3935853460303965</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1762054440065146</v>
+        <v>0.1781054440065146</v>
       </c>
       <c r="C67">
-        <v>-22.07299824545848</v>
+        <v>-25.08621213124354</v>
       </c>
       <c r="D67">
-        <v>95.00200175454154</v>
+        <v>94.14378786875648</v>
       </c>
       <c r="E67">
-        <v>125.075</v>
+        <v>127.23</v>
       </c>
       <c r="F67">
-        <v>140.075</v>
+        <v>142.23</v>
       </c>
       <c r="G67">
         <v>23</v>
@@ -6781,37 +6781,37 @@
         <v>13</v>
       </c>
       <c r="M67">
-        <v>33.02968500000001</v>
+        <v>33.537834</v>
       </c>
       <c r="N67">
-        <v>-20.02968500000001</v>
+        <v>-20.537834</v>
       </c>
       <c r="O67">
-        <v>-5.608311800000003</v>
+        <v>-5.750593520000002</v>
       </c>
       <c r="P67">
-        <v>-14.4213732</v>
+        <v>-14.78724048</v>
       </c>
       <c r="Q67">
-        <v>35.5786268</v>
+        <v>35.21275952</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1137897008074762</v>
+        <v>0.115789397890049</v>
       </c>
       <c r="T67">
-        <v>1.570200942435939</v>
+        <v>1.61638332309582</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.110203896888511</v>
+        <v>0.1085341408750487</v>
       </c>
       <c r="W67">
-        <v>0.2098139211136891</v>
+        <v>0.2102076495816635</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3935853460303965</v>
+        <v>0.3876219316966026</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1781054440065146</v>
+        <v>0.1800054440065146</v>
       </c>
       <c r="C68">
-        <v>-25.08621213124354</v>
+        <v>-28.08405924429947</v>
       </c>
       <c r="D68">
-        <v>94.14378786875648</v>
+        <v>93.30094075570055</v>
       </c>
       <c r="E68">
-        <v>127.23</v>
+        <v>129.385</v>
       </c>
       <c r="F68">
-        <v>142.23</v>
+        <v>144.385</v>
       </c>
       <c r="G68">
         <v>23</v>
@@ -6863,37 +6863,37 @@
         <v>13</v>
       </c>
       <c r="M68">
-        <v>33.537834</v>
+        <v>34.04598300000001</v>
       </c>
       <c r="N68">
-        <v>-20.537834</v>
+        <v>-21.04598300000001</v>
       </c>
       <c r="O68">
-        <v>-5.750593520000002</v>
+        <v>-5.892875240000002</v>
       </c>
       <c r="P68">
-        <v>-14.78724048</v>
+        <v>-15.15310776</v>
       </c>
       <c r="Q68">
-        <v>35.21275952</v>
+        <v>34.84689224</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.115789397890049</v>
+        <v>0.117910288735202</v>
       </c>
       <c r="T68">
-        <v>1.61638332309582</v>
+        <v>1.665364635916905</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1085341408750487</v>
+        <v>0.1069142283246749</v>
       </c>
       <c r="W68">
-        <v>0.2102076495816635</v>
+        <v>0.2105896249610417</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3876219316966026</v>
+        <v>0.3818365297309817</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1800054440065146</v>
+        <v>0.1819054440065146</v>
       </c>
       <c r="C69">
-        <v>-28.08405924429947</v>
+        <v>-31.06694864764975</v>
       </c>
       <c r="D69">
-        <v>93.30094075570055</v>
+        <v>92.47305135235027</v>
       </c>
       <c r="E69">
-        <v>129.385</v>
+        <v>131.54</v>
       </c>
       <c r="F69">
-        <v>144.385</v>
+        <v>146.54</v>
       </c>
       <c r="G69">
         <v>23</v>
@@ -6945,37 +6945,37 @@
         <v>13</v>
       </c>
       <c r="M69">
-        <v>34.04598300000001</v>
+        <v>34.554132</v>
       </c>
       <c r="N69">
-        <v>-21.04598300000001</v>
+        <v>-21.554132</v>
       </c>
       <c r="O69">
-        <v>-5.892875240000002</v>
+        <v>-6.035156960000001</v>
       </c>
       <c r="P69">
-        <v>-15.15310776</v>
+        <v>-15.51897504</v>
       </c>
       <c r="Q69">
-        <v>34.84689224</v>
+        <v>34.48102496</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.117910288735202</v>
+        <v>0.1201637352581771</v>
       </c>
       <c r="T69">
-        <v>1.665364635916905</v>
+        <v>1.717407280789309</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1069142283246749</v>
+        <v>0.1053419602610767</v>
       </c>
       <c r="W69">
-        <v>0.2105896249610417</v>
+        <v>0.2109603657704381</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3818365297309817</v>
+        <v>0.3762212866467026</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1819054440065146</v>
+        <v>0.1838054440065146</v>
       </c>
       <c r="C70">
-        <v>-31.06694864764975</v>
+        <v>-34.03527501302283</v>
       </c>
       <c r="D70">
-        <v>92.47305135235027</v>
+        <v>91.6597249869772</v>
       </c>
       <c r="E70">
-        <v>131.54</v>
+        <v>133.695</v>
       </c>
       <c r="F70">
-        <v>146.54</v>
+        <v>148.695</v>
       </c>
       <c r="G70">
         <v>23</v>
@@ -7027,37 +7027,37 @@
         <v>13</v>
       </c>
       <c r="M70">
-        <v>34.554132</v>
+        <v>35.06228100000001</v>
       </c>
       <c r="N70">
-        <v>-21.554132</v>
+        <v>-22.06228100000001</v>
       </c>
       <c r="O70">
-        <v>-6.035156960000001</v>
+        <v>-6.177438680000003</v>
       </c>
       <c r="P70">
-        <v>-15.51897504</v>
+        <v>-15.88484232</v>
       </c>
       <c r="Q70">
-        <v>34.48102496</v>
+        <v>34.11515768</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1201637352581771</v>
+        <v>0.1225625654277957</v>
       </c>
       <c r="T70">
-        <v>1.717407280789309</v>
+        <v>1.77280751565348</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1053419602610767</v>
+        <v>0.1038152651848292</v>
       </c>
       <c r="W70">
-        <v>0.2109603657704381</v>
+        <v>0.2113203604694173</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3762212866467026</v>
+        <v>0.3707688042315329</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1838054440065146</v>
+        <v>0.1857054440065146</v>
       </c>
       <c r="C71">
-        <v>-34.03527501302283</v>
+        <v>-36.98941924821149</v>
       </c>
       <c r="D71">
-        <v>91.6597249869772</v>
+        <v>90.86058075178853</v>
       </c>
       <c r="E71">
-        <v>133.695</v>
+        <v>135.85</v>
       </c>
       <c r="F71">
-        <v>148.695</v>
+        <v>150.85</v>
       </c>
       <c r="G71">
         <v>23</v>
@@ -7109,37 +7109,37 @@
         <v>13</v>
       </c>
       <c r="M71">
-        <v>35.06228100000001</v>
+        <v>35.57043000000001</v>
       </c>
       <c r="N71">
-        <v>-22.06228100000001</v>
+        <v>-22.57043000000001</v>
       </c>
       <c r="O71">
-        <v>-6.177438680000003</v>
+        <v>-6.319720400000003</v>
       </c>
       <c r="P71">
-        <v>-15.88484232</v>
+        <v>-16.25070960000001</v>
       </c>
       <c r="Q71">
-        <v>34.11515768</v>
+        <v>33.74929039999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1225625654277957</v>
+        <v>0.1251213176087222</v>
       </c>
       <c r="T71">
-        <v>1.77280751565348</v>
+        <v>1.831901099508596</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1038152651848292</v>
+        <v>0.1023321899679031</v>
       </c>
       <c r="W71">
-        <v>0.2113203604694173</v>
+        <v>0.2116700696055685</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3707688042315329</v>
+        <v>0.3654721070282253</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1857054440065146</v>
+        <v>0.1876054440065146</v>
       </c>
       <c r="C72">
-        <v>-36.98941924821149</v>
+        <v>-39.92974909189813</v>
       </c>
       <c r="D72">
-        <v>90.86058075178853</v>
+        <v>90.07525090810189</v>
       </c>
       <c r="E72">
-        <v>135.85</v>
+        <v>138.005</v>
       </c>
       <c r="F72">
-        <v>150.85</v>
+        <v>153.005</v>
       </c>
       <c r="G72">
         <v>23</v>
@@ -7191,37 +7191,37 @@
         <v>13</v>
       </c>
       <c r="M72">
-        <v>35.57043000000001</v>
+        <v>36.078579</v>
       </c>
       <c r="N72">
-        <v>-22.57043000000001</v>
+        <v>-23.078579</v>
       </c>
       <c r="O72">
-        <v>-6.319720400000003</v>
+        <v>-6.462002120000002</v>
       </c>
       <c r="P72">
-        <v>-16.25070960000001</v>
+        <v>-16.61657688</v>
       </c>
       <c r="Q72">
-        <v>33.74929039999999</v>
+        <v>33.38342312</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1251213176087222</v>
+        <v>0.1278565354572988</v>
       </c>
       <c r="T72">
-        <v>1.831901099508596</v>
+        <v>1.895070102939927</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1023321899679031</v>
+        <v>0.100890891517651</v>
       </c>
       <c r="W72">
-        <v>0.2116700696055685</v>
+        <v>0.2120099277801379</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3654721070282253</v>
+        <v>0.360324612563039</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1876054440065146</v>
+        <v>0.1895054440065146</v>
       </c>
       <c r="C73">
-        <v>-39.9297490918981</v>
+        <v>-42.85661967789659</v>
       </c>
       <c r="D73">
-        <v>90.07525090810189</v>
+        <v>89.30338032210341</v>
       </c>
       <c r="E73">
-        <v>138.005</v>
+        <v>140.16</v>
       </c>
       <c r="F73">
-        <v>153.005</v>
+        <v>155.16</v>
       </c>
       <c r="G73">
         <v>23</v>
@@ -7273,37 +7273,37 @@
         <v>13</v>
       </c>
       <c r="M73">
-        <v>36.078579</v>
+        <v>36.586728</v>
       </c>
       <c r="N73">
-        <v>-23.078579</v>
+        <v>-23.586728</v>
       </c>
       <c r="O73">
-        <v>-6.46200212</v>
+        <v>-6.604283840000001</v>
       </c>
       <c r="P73">
-        <v>-16.61657688</v>
+        <v>-16.98244416</v>
       </c>
       <c r="Q73">
-        <v>33.38342312</v>
+        <v>33.01755584</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1278565354572988</v>
+        <v>0.1307871260093452</v>
       </c>
       <c r="T73">
-        <v>1.895070102939926</v>
+        <v>1.962751178044924</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.100890891517651</v>
+        <v>0.09948962913546136</v>
       </c>
       <c r="W73">
-        <v>0.2120099277801379</v>
+        <v>0.2123403454498582</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3603246125630392</v>
+        <v>0.3553201040552192</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1895054440065146</v>
+        <v>0.1914054440065145</v>
       </c>
       <c r="C74">
-        <v>-42.85661967789659</v>
+        <v>-45.77037407063035</v>
       </c>
       <c r="D74">
-        <v>89.30338032210341</v>
+        <v>88.54462592936964</v>
       </c>
       <c r="E74">
-        <v>140.16</v>
+        <v>142.315</v>
       </c>
       <c r="F74">
-        <v>155.16</v>
+        <v>157.315</v>
       </c>
       <c r="G74">
         <v>23</v>
@@ -7355,37 +7355,37 @@
         <v>13</v>
       </c>
       <c r="M74">
-        <v>36.586728</v>
+        <v>37.094877</v>
       </c>
       <c r="N74">
-        <v>-23.586728</v>
+        <v>-24.094877</v>
       </c>
       <c r="O74">
-        <v>-6.604283840000001</v>
+        <v>-6.746565560000001</v>
       </c>
       <c r="P74">
-        <v>-16.98244416</v>
+        <v>-17.34831144</v>
       </c>
       <c r="Q74">
-        <v>33.01755584</v>
+        <v>32.65168856</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1307871260093452</v>
+        <v>0.1339347973430246</v>
       </c>
       <c r="T74">
-        <v>1.962751178044924</v>
+        <v>2.035445666120661</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09948962913546136</v>
+        <v>0.09812675750346873</v>
       </c>
       <c r="W74">
-        <v>0.2123403454498582</v>
+        <v>0.2126617105806821</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3553201040552192</v>
+        <v>0.3504527053695312</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1914054440065145</v>
+        <v>0.1933054440065146</v>
       </c>
       <c r="C75">
-        <v>-45.77037407063035</v>
+        <v>-48.6713437735427</v>
       </c>
       <c r="D75">
-        <v>88.54462592936964</v>
+        <v>87.7986562264573</v>
       </c>
       <c r="E75">
-        <v>142.315</v>
+        <v>144.47</v>
       </c>
       <c r="F75">
-        <v>157.315</v>
+        <v>159.47</v>
       </c>
       <c r="G75">
         <v>23</v>
@@ -7437,37 +7437,37 @@
         <v>13</v>
       </c>
       <c r="M75">
-        <v>37.094877</v>
+        <v>37.603026</v>
       </c>
       <c r="N75">
-        <v>-24.094877</v>
+        <v>-24.603026</v>
       </c>
       <c r="O75">
-        <v>-6.746565560000001</v>
+        <v>-6.88884728</v>
       </c>
       <c r="P75">
-        <v>-17.34831144</v>
+        <v>-17.71417872</v>
       </c>
       <c r="Q75">
-        <v>32.65168856</v>
+        <v>32.28582128</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1339347973430246</v>
+        <v>0.1373245972408333</v>
       </c>
       <c r="T75">
-        <v>2.035445666120661</v>
+        <v>2.113732037894533</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09812675750346873</v>
+        <v>0.09680072023990835</v>
       </c>
       <c r="W75">
-        <v>0.2126617105806821</v>
+        <v>0.2129743901674296</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3504527053695312</v>
+        <v>0.3457168579996727</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1933054440065146</v>
+        <v>0.1952054440065146</v>
       </c>
       <c r="C76">
-        <v>-48.6713437735427</v>
+        <v>-51.55984921202221</v>
       </c>
       <c r="D76">
-        <v>87.7986562264573</v>
+        <v>87.06515078797779</v>
       </c>
       <c r="E76">
-        <v>144.47</v>
+        <v>146.625</v>
       </c>
       <c r="F76">
-        <v>159.47</v>
+        <v>161.625</v>
       </c>
       <c r="G76">
         <v>23</v>
@@ -7519,37 +7519,37 @@
         <v>13</v>
       </c>
       <c r="M76">
-        <v>37.603026</v>
+        <v>38.111175</v>
       </c>
       <c r="N76">
-        <v>-24.603026</v>
+        <v>-25.111175</v>
       </c>
       <c r="O76">
-        <v>-6.88884728</v>
+        <v>-7.031129000000002</v>
       </c>
       <c r="P76">
-        <v>-17.71417872</v>
+        <v>-18.080046</v>
       </c>
       <c r="Q76">
-        <v>32.28582128</v>
+        <v>31.919954</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1373245972408333</v>
+        <v>0.1409855811304666</v>
       </c>
       <c r="T76">
-        <v>2.113732037894533</v>
+        <v>2.198281319410315</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09680072023990835</v>
+        <v>0.09551004397004291</v>
       </c>
       <c r="W76">
-        <v>0.2129743901674296</v>
+        <v>0.2132787316318639</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3457168579996727</v>
+        <v>0.3411072998930104</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1952054440065146</v>
+        <v>0.1971054440065146</v>
       </c>
       <c r="C77">
-        <v>-51.55984921202221</v>
+        <v>-54.43620019232151</v>
       </c>
       <c r="D77">
-        <v>87.06515078797779</v>
+        <v>86.34379980767849</v>
       </c>
       <c r="E77">
-        <v>146.625</v>
+        <v>148.78</v>
       </c>
       <c r="F77">
-        <v>161.625</v>
+        <v>163.78</v>
       </c>
       <c r="G77">
         <v>23</v>
@@ -7601,37 +7601,37 @@
         <v>13</v>
       </c>
       <c r="M77">
-        <v>38.111175</v>
+        <v>38.619324</v>
       </c>
       <c r="N77">
-        <v>-25.111175</v>
+        <v>-25.619324</v>
       </c>
       <c r="O77">
-        <v>-7.031129000000002</v>
+        <v>-7.173410720000001</v>
       </c>
       <c r="P77">
-        <v>-18.080046</v>
+        <v>-18.44591328</v>
       </c>
       <c r="Q77">
-        <v>31.919954</v>
+        <v>31.55408672</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1409855811304666</v>
+        <v>0.1449516470109027</v>
       </c>
       <c r="T77">
-        <v>2.198281319410315</v>
+        <v>2.289876374385745</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09551004397004291</v>
+        <v>0.09425333286517393</v>
       </c>
       <c r="W77">
-        <v>0.2132787316318639</v>
+        <v>0.213575064110392</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3411072998930104</v>
+        <v>0.3366190459470497</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1971054440065146</v>
+        <v>0.1990054440065146</v>
       </c>
       <c r="C78">
-        <v>-54.43620019232151</v>
+        <v>-57.30069633785017</v>
       </c>
       <c r="D78">
-        <v>86.34379980767849</v>
+        <v>85.63430366214983</v>
       </c>
       <c r="E78">
-        <v>148.78</v>
+        <v>150.935</v>
       </c>
       <c r="F78">
-        <v>163.78</v>
+        <v>165.935</v>
       </c>
       <c r="G78">
         <v>23</v>
@@ -7683,37 +7683,37 @@
         <v>13</v>
       </c>
       <c r="M78">
-        <v>38.619324</v>
+        <v>39.127473</v>
       </c>
       <c r="N78">
-        <v>-25.619324</v>
+        <v>-26.127473</v>
       </c>
       <c r="O78">
-        <v>-7.173410720000001</v>
+        <v>-7.315692440000001</v>
       </c>
       <c r="P78">
-        <v>-18.44591328</v>
+        <v>-18.81178056</v>
       </c>
       <c r="Q78">
-        <v>31.55408672</v>
+        <v>31.18821944</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1449516470109027</v>
+        <v>0.1492625881852898</v>
       </c>
       <c r="T78">
-        <v>2.289876374385745</v>
+        <v>2.389436216750342</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09425333286517393</v>
+        <v>0.09302926360718466</v>
       </c>
       <c r="W78">
-        <v>0.213575064110392</v>
+        <v>0.2138636996414259</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3366190459470497</v>
+        <v>0.3322473700256594</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1990054440065146</v>
+        <v>0.2009054440065146</v>
       </c>
       <c r="C79">
-        <v>-57.30069633785017</v>
+        <v>-60.15362750413229</v>
       </c>
       <c r="D79">
-        <v>85.63430366214983</v>
+        <v>84.93637249586772</v>
       </c>
       <c r="E79">
-        <v>150.935</v>
+        <v>153.09</v>
       </c>
       <c r="F79">
-        <v>165.935</v>
+        <v>168.09</v>
       </c>
       <c r="G79">
         <v>23</v>
@@ -7765,37 +7765,37 @@
         <v>13</v>
       </c>
       <c r="M79">
-        <v>39.127473</v>
+        <v>39.63562200000001</v>
       </c>
       <c r="N79">
-        <v>-26.127473</v>
+        <v>-26.63562200000001</v>
       </c>
       <c r="O79">
-        <v>-7.315692440000001</v>
+        <v>-7.457974160000002</v>
       </c>
       <c r="P79">
-        <v>-18.81178056</v>
+        <v>-19.17764784</v>
       </c>
       <c r="Q79">
-        <v>31.18821944</v>
+        <v>30.82235216</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1492625881852898</v>
+        <v>0.153965433102803</v>
       </c>
       <c r="T79">
-        <v>2.389436216750342</v>
+        <v>2.498046953875358</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09302926360718466</v>
+        <v>0.09183658074042586</v>
       </c>
       <c r="W79">
-        <v>0.2138636996414259</v>
+        <v>0.2141449342614076</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3322473700256594</v>
+        <v>0.3279877883586638</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2009054440065146</v>
+        <v>0.2028054440065146</v>
       </c>
       <c r="C80">
-        <v>-60.15362750413229</v>
+        <v>-62.9952741736367</v>
       </c>
       <c r="D80">
-        <v>84.93637249586772</v>
+        <v>84.2497258263633</v>
       </c>
       <c r="E80">
-        <v>153.09</v>
+        <v>155.245</v>
       </c>
       <c r="F80">
-        <v>168.09</v>
+        <v>170.245</v>
       </c>
       <c r="G80">
         <v>23</v>
@@ -7847,37 +7847,37 @@
         <v>13</v>
       </c>
       <c r="M80">
-        <v>39.63562200000001</v>
+        <v>40.143771</v>
       </c>
       <c r="N80">
-        <v>-26.63562200000001</v>
+        <v>-27.143771</v>
       </c>
       <c r="O80">
-        <v>-7.457974160000002</v>
+        <v>-7.600255880000001</v>
       </c>
       <c r="P80">
-        <v>-19.17764784</v>
+        <v>-19.54351512</v>
       </c>
       <c r="Q80">
-        <v>30.82235216</v>
+        <v>30.45648488</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.153965433102803</v>
+        <v>0.1591161680124603</v>
       </c>
       <c r="T80">
-        <v>2.498046953875358</v>
+        <v>2.617001570726565</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09183658074042586</v>
+        <v>0.09067409237662302</v>
       </c>
       <c r="W80">
-        <v>0.2141449342614076</v>
+        <v>0.2144190490175923</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3279877883586638</v>
+        <v>0.323836044202225</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2028054440065146</v>
+        <v>0.2047054440065146</v>
       </c>
       <c r="C81">
-        <v>-62.9952741736367</v>
+        <v>-65.82590783160899</v>
       </c>
       <c r="D81">
-        <v>84.2497258263633</v>
+        <v>83.57409216839102</v>
       </c>
       <c r="E81">
-        <v>155.245</v>
+        <v>157.4</v>
       </c>
       <c r="F81">
-        <v>170.245</v>
+        <v>172.4</v>
       </c>
       <c r="G81">
         <v>23</v>
@@ -7929,37 +7929,37 @@
         <v>13</v>
       </c>
       <c r="M81">
-        <v>40.143771</v>
+        <v>40.65192</v>
       </c>
       <c r="N81">
-        <v>-27.143771</v>
+        <v>-27.65192</v>
       </c>
       <c r="O81">
-        <v>-7.600255880000001</v>
+        <v>-7.742537600000002</v>
       </c>
       <c r="P81">
-        <v>-19.54351512</v>
+        <v>-19.9093824</v>
       </c>
       <c r="Q81">
-        <v>30.45648488</v>
+        <v>30.0906176</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1591161680124603</v>
+        <v>0.1647819764130833</v>
       </c>
       <c r="T81">
-        <v>2.617001570726565</v>
+        <v>2.747851649262894</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09067409237662302</v>
+        <v>0.08954066622191521</v>
       </c>
       <c r="W81">
-        <v>0.2144190490175923</v>
+        <v>0.2146863109048724</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.323836044202225</v>
+        <v>0.3197880936496972</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2047054440065146</v>
+        <v>0.2066054440065146</v>
       </c>
       <c r="C82">
-        <v>-65.82590783160899</v>
+        <v>-68.64579132396391</v>
       </c>
       <c r="D82">
-        <v>83.57409216839102</v>
+        <v>82.9092086760361</v>
       </c>
       <c r="E82">
-        <v>157.4</v>
+        <v>159.555</v>
       </c>
       <c r="F82">
-        <v>172.4</v>
+        <v>174.555</v>
       </c>
       <c r="G82">
         <v>23</v>
@@ -8011,37 +8011,37 @@
         <v>13</v>
       </c>
       <c r="M82">
-        <v>40.65192</v>
+        <v>41.160069</v>
       </c>
       <c r="N82">
-        <v>-27.65192</v>
+        <v>-28.160069</v>
       </c>
       <c r="O82">
-        <v>-7.742537600000002</v>
+        <v>-7.884819320000001</v>
       </c>
       <c r="P82">
-        <v>-19.9093824</v>
+        <v>-20.27524968</v>
       </c>
       <c r="Q82">
-        <v>30.0906176</v>
+        <v>29.72475032</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1647819764130833</v>
+        <v>0.1710441856979824</v>
       </c>
       <c r="T82">
-        <v>2.747851649262894</v>
+        <v>2.89247542027673</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08954066622191521</v>
+        <v>0.08843522589818788</v>
       </c>
       <c r="W82">
-        <v>0.2146863109048724</v>
+        <v>0.2149469737332073</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3197880936496972</v>
+        <v>0.3158400924935282</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2066054440065146</v>
+        <v>0.2085054440065146</v>
       </c>
       <c r="C83">
-        <v>-68.64579132396391</v>
+        <v>-71.45517919822903</v>
       </c>
       <c r="D83">
-        <v>82.9092086760361</v>
+        <v>82.25482080177098</v>
       </c>
       <c r="E83">
-        <v>159.555</v>
+        <v>161.71</v>
       </c>
       <c r="F83">
-        <v>174.555</v>
+        <v>176.71</v>
       </c>
       <c r="G83">
         <v>23</v>
@@ -8093,37 +8093,37 @@
         <v>13</v>
       </c>
       <c r="M83">
-        <v>41.160069</v>
+        <v>41.668218</v>
       </c>
       <c r="N83">
-        <v>-28.160069</v>
+        <v>-28.668218</v>
       </c>
       <c r="O83">
-        <v>-7.884819320000001</v>
+        <v>-8.027101040000002</v>
       </c>
       <c r="P83">
-        <v>-20.27524968</v>
+        <v>-20.64111696</v>
       </c>
       <c r="Q83">
-        <v>29.72475032</v>
+        <v>29.35888304</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1710441856979824</v>
+        <v>0.178002196014537</v>
       </c>
       <c r="T83">
-        <v>2.89247542027673</v>
+        <v>3.053168499180994</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08843522589818788</v>
+        <v>0.08735674753357582</v>
       </c>
       <c r="W83">
-        <v>0.2149469737332073</v>
+        <v>0.2152012789315828</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3158400924935282</v>
+        <v>0.3119883840484851</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2085054440065146</v>
+        <v>0.2104054440065146</v>
       </c>
       <c r="C84">
-        <v>-71.45517919822903</v>
+        <v>-74.25431802846869</v>
       </c>
       <c r="D84">
-        <v>82.25482080177098</v>
+        <v>81.61068197153132</v>
       </c>
       <c r="E84">
-        <v>161.71</v>
+        <v>163.865</v>
       </c>
       <c r="F84">
-        <v>176.71</v>
+        <v>178.865</v>
       </c>
       <c r="G84">
         <v>23</v>
@@ -8175,37 +8175,37 @@
         <v>13</v>
       </c>
       <c r="M84">
-        <v>41.668218</v>
+        <v>42.17636700000001</v>
       </c>
       <c r="N84">
-        <v>-28.668218</v>
+        <v>-29.17636700000001</v>
       </c>
       <c r="O84">
-        <v>-8.027101040000002</v>
+        <v>-8.169382760000003</v>
       </c>
       <c r="P84">
-        <v>-20.64111696</v>
+        <v>-21.00698424</v>
       </c>
       <c r="Q84">
-        <v>29.35888304</v>
+        <v>28.99301576</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.178002196014537</v>
+        <v>0.185778795780098</v>
       </c>
       <c r="T84">
-        <v>3.053168499180994</v>
+        <v>3.23276664619164</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08735674753357582</v>
+        <v>0.08630425659943636</v>
       </c>
       <c r="W84">
-        <v>0.2152012789315828</v>
+        <v>0.2154494562938529</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3119883840484851</v>
+        <v>0.3082294878551298</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2104054440065146</v>
+        <v>0.2123054440065146</v>
       </c>
       <c r="C85">
-        <v>-74.25431802846869</v>
+        <v>-77.04344672505975</v>
       </c>
       <c r="D85">
-        <v>81.61068197153132</v>
+        <v>80.97655327494026</v>
       </c>
       <c r="E85">
-        <v>163.865</v>
+        <v>166.02</v>
       </c>
       <c r="F85">
-        <v>178.865</v>
+        <v>181.02</v>
       </c>
       <c r="G85">
         <v>23</v>
@@ -8257,37 +8257,37 @@
         <v>13</v>
       </c>
       <c r="M85">
-        <v>42.17636700000001</v>
+        <v>42.684516</v>
       </c>
       <c r="N85">
-        <v>-29.17636700000001</v>
+        <v>-29.684516</v>
       </c>
       <c r="O85">
-        <v>-8.169382760000003</v>
+        <v>-8.311664480000001</v>
       </c>
       <c r="P85">
-        <v>-21.00698424</v>
+        <v>-21.37285152</v>
       </c>
       <c r="Q85">
-        <v>28.99301576</v>
+        <v>28.62714848</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.185778795780098</v>
+        <v>0.1945274705163542</v>
       </c>
       <c r="T85">
-        <v>3.23276664619164</v>
+        <v>3.434814561578619</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08630425659943636</v>
+        <v>0.0852768249732526</v>
       </c>
       <c r="W85">
-        <v>0.2154494562938529</v>
+        <v>0.215691724671307</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3082294878551298</v>
+        <v>0.3045600891901878</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2123054440065145</v>
+        <v>0.2142054440065146</v>
       </c>
       <c r="C86">
-        <v>-77.04344672505972</v>
+        <v>-79.82279683013665</v>
       </c>
       <c r="D86">
-        <v>80.97655327494026</v>
+        <v>80.35220316986333</v>
       </c>
       <c r="E86">
-        <v>166.02</v>
+        <v>168.175</v>
       </c>
       <c r="F86">
-        <v>181.02</v>
+        <v>183.175</v>
       </c>
       <c r="G86">
         <v>23</v>
@@ -8339,37 +8339,37 @@
         <v>13</v>
       </c>
       <c r="M86">
-        <v>42.684516</v>
+        <v>43.192665</v>
       </c>
       <c r="N86">
-        <v>-29.684516</v>
+        <v>-30.192665</v>
       </c>
       <c r="O86">
-        <v>-8.311664479999999</v>
+        <v>-8.453946200000001</v>
       </c>
       <c r="P86">
-        <v>-21.37285152</v>
+        <v>-21.7387188</v>
       </c>
       <c r="Q86">
-        <v>28.62714848</v>
+        <v>28.2612812</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1945274705163541</v>
+        <v>0.2044426352174444</v>
       </c>
       <c r="T86">
-        <v>3.434814561578616</v>
+        <v>3.663802199017191</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08527682497325262</v>
+        <v>0.08427356820886141</v>
       </c>
       <c r="W86">
-        <v>0.215691724671307</v>
+        <v>0.2159282926163505</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3045600891901878</v>
+        <v>0.3009770293173621</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2142054440065146</v>
+        <v>0.2161054440065145</v>
       </c>
       <c r="C87">
-        <v>-79.82279683013665</v>
+        <v>-82.59259279947332</v>
       </c>
       <c r="D87">
-        <v>80.35220316986333</v>
+        <v>79.73740720052666</v>
       </c>
       <c r="E87">
-        <v>168.175</v>
+        <v>170.33</v>
       </c>
       <c r="F87">
-        <v>183.175</v>
+        <v>185.33</v>
       </c>
       <c r="G87">
         <v>23</v>
@@ -8421,37 +8421,37 @@
         <v>13</v>
       </c>
       <c r="M87">
-        <v>43.192665</v>
+        <v>43.700814</v>
       </c>
       <c r="N87">
-        <v>-30.192665</v>
+        <v>-30.700814</v>
       </c>
       <c r="O87">
-        <v>-8.453946200000001</v>
+        <v>-8.59622792</v>
       </c>
       <c r="P87">
-        <v>-21.7387188</v>
+        <v>-22.10458608</v>
       </c>
       <c r="Q87">
-        <v>28.2612812</v>
+        <v>27.89541392</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2044426352174444</v>
+        <v>0.2157742520186904</v>
       </c>
       <c r="T87">
-        <v>3.663802199017191</v>
+        <v>3.925502356089848</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08427356820886141</v>
+        <v>0.08329364299713045</v>
       </c>
       <c r="W87">
-        <v>0.2159282926163505</v>
+        <v>0.2161593589812766</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3009770293173621</v>
+        <v>0.297477296418323</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2161054440065145</v>
+        <v>0.2180054440065146</v>
       </c>
       <c r="C88">
-        <v>-82.59259279947332</v>
+        <v>-85.3530522715227</v>
       </c>
       <c r="D88">
-        <v>79.73740720052666</v>
+        <v>79.13194772847729</v>
       </c>
       <c r="E88">
-        <v>170.33</v>
+        <v>172.485</v>
       </c>
       <c r="F88">
-        <v>185.33</v>
+        <v>187.485</v>
       </c>
       <c r="G88">
         <v>23</v>
@@ -8503,37 +8503,37 @@
         <v>13</v>
       </c>
       <c r="M88">
-        <v>43.700814</v>
+        <v>44.208963</v>
       </c>
       <c r="N88">
-        <v>-30.700814</v>
+        <v>-31.208963</v>
       </c>
       <c r="O88">
-        <v>-8.59622792</v>
+        <v>-8.73850964</v>
       </c>
       <c r="P88">
-        <v>-22.10458608</v>
+        <v>-22.47045336</v>
       </c>
       <c r="Q88">
-        <v>27.89541392</v>
+        <v>27.52954664</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2157742520186904</v>
+        <v>0.2288491944816665</v>
       </c>
       <c r="T88">
-        <v>3.925502356089848</v>
+        <v>4.227464075789066</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08329364299713045</v>
+        <v>0.08233624480176115</v>
       </c>
       <c r="W88">
-        <v>0.2161593589812766</v>
+        <v>0.2163851134757447</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.297477296418323</v>
+        <v>0.2940580171491469</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2180054440065146</v>
+        <v>0.2199054440065146</v>
       </c>
       <c r="C89">
-        <v>-85.3530522715227</v>
+        <v>-88.10438632429154</v>
       </c>
       <c r="D89">
-        <v>79.13194772847729</v>
+        <v>78.53561367570848</v>
       </c>
       <c r="E89">
-        <v>172.485</v>
+        <v>174.64</v>
       </c>
       <c r="F89">
-        <v>187.485</v>
+        <v>189.64</v>
       </c>
       <c r="G89">
         <v>23</v>
@@ -8585,37 +8585,37 @@
         <v>13</v>
       </c>
       <c r="M89">
-        <v>44.208963</v>
+        <v>44.71711200000001</v>
       </c>
       <c r="N89">
-        <v>-31.208963</v>
+        <v>-31.71711200000001</v>
       </c>
       <c r="O89">
-        <v>-8.73850964</v>
+        <v>-8.880791360000003</v>
       </c>
       <c r="P89">
-        <v>-22.47045336</v>
+        <v>-22.83632064</v>
       </c>
       <c r="Q89">
-        <v>27.52954664</v>
+        <v>27.16367936</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2288491944816665</v>
+        <v>0.2441032940218054</v>
       </c>
       <c r="T89">
-        <v>4.227464075789066</v>
+        <v>4.579752748771489</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08233624480176115</v>
+        <v>0.08140060565628657</v>
       </c>
       <c r="W89">
-        <v>0.2163851134757447</v>
+        <v>0.2166057371862476</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2940580171491469</v>
+        <v>0.290716448772452</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2199054440065146</v>
+        <v>0.2218054440065146</v>
       </c>
       <c r="C90">
-        <v>-88.10438632429154</v>
+        <v>-90.84679972068734</v>
       </c>
       <c r="D90">
-        <v>78.53561367570848</v>
+        <v>77.94820027931267</v>
       </c>
       <c r="E90">
-        <v>174.64</v>
+        <v>176.795</v>
       </c>
       <c r="F90">
-        <v>189.64</v>
+        <v>191.795</v>
       </c>
       <c r="G90">
         <v>23</v>
@@ -8667,37 +8667,37 @@
         <v>13</v>
       </c>
       <c r="M90">
-        <v>44.71711200000001</v>
+        <v>45.225261</v>
       </c>
       <c r="N90">
-        <v>-31.71711200000001</v>
+        <v>-32.225261</v>
       </c>
       <c r="O90">
-        <v>-8.880791360000003</v>
+        <v>-9.023073080000001</v>
       </c>
       <c r="P90">
-        <v>-22.83632064</v>
+        <v>-23.20218792</v>
       </c>
       <c r="Q90">
-        <v>27.16367936</v>
+        <v>26.79781208</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2441032940218054</v>
+        <v>0.2621308662056059</v>
       </c>
       <c r="T90">
-        <v>4.579752748771489</v>
+        <v>4.996093907750716</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08140060565628657</v>
+        <v>0.08048599210958673</v>
       </c>
       <c r="W90">
-        <v>0.2166057371862476</v>
+        <v>0.2168214030605595</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.290716448772452</v>
+        <v>0.2874499718199526</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2218054440065146</v>
+        <v>0.2237054440065146</v>
       </c>
       <c r="C91">
-        <v>-90.84679972068734</v>
+        <v>-93.58049114293642</v>
       </c>
       <c r="D91">
-        <v>77.94820027931267</v>
+        <v>77.36950885706359</v>
       </c>
       <c r="E91">
-        <v>176.795</v>
+        <v>178.95</v>
       </c>
       <c r="F91">
-        <v>191.795</v>
+        <v>193.95</v>
       </c>
       <c r="G91">
         <v>23</v>
@@ -8749,37 +8749,37 @@
         <v>13</v>
       </c>
       <c r="M91">
-        <v>45.225261</v>
+        <v>45.73341000000001</v>
       </c>
       <c r="N91">
-        <v>-32.225261</v>
+        <v>-32.73341000000001</v>
       </c>
       <c r="O91">
-        <v>-9.023073080000001</v>
+        <v>-9.165354800000003</v>
       </c>
       <c r="P91">
-        <v>-23.20218792</v>
+        <v>-23.5680552</v>
       </c>
       <c r="Q91">
-        <v>26.79781208</v>
+        <v>26.4319448</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2621308662056059</v>
+        <v>0.2837639528261666</v>
       </c>
       <c r="T91">
-        <v>4.996093907750716</v>
+        <v>5.495703298525789</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08048599210958673</v>
+        <v>0.07959170330836909</v>
       </c>
       <c r="W91">
-        <v>0.2168214030605595</v>
+        <v>0.2170322763598866</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2874499718199526</v>
+        <v>0.2842560832441753</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2237054440065146</v>
+        <v>0.2256054440065146</v>
       </c>
       <c r="C92">
-        <v>-93.58049114293642</v>
+        <v>-96.30565341663709</v>
       </c>
       <c r="D92">
-        <v>77.36950885706359</v>
+        <v>76.79934658336293</v>
       </c>
       <c r="E92">
-        <v>178.95</v>
+        <v>181.105</v>
       </c>
       <c r="F92">
-        <v>193.95</v>
+        <v>196.105</v>
       </c>
       <c r="G92">
         <v>23</v>
@@ -8831,37 +8831,37 @@
         <v>13</v>
       </c>
       <c r="M92">
-        <v>45.73341000000001</v>
+        <v>46.24155900000001</v>
       </c>
       <c r="N92">
-        <v>-32.73341000000001</v>
+        <v>-33.24155900000001</v>
       </c>
       <c r="O92">
-        <v>-9.165354800000003</v>
+        <v>-9.307636520000003</v>
       </c>
       <c r="P92">
-        <v>-23.5680552</v>
+        <v>-23.93392248000001</v>
       </c>
       <c r="Q92">
-        <v>26.4319448</v>
+        <v>26.06607751999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2837639528261666</v>
+        <v>0.310204392029074</v>
       </c>
       <c r="T92">
-        <v>5.495703298525789</v>
+        <v>6.106336998361988</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07959170330836909</v>
+        <v>0.07871706920607931</v>
       </c>
       <c r="W92">
-        <v>0.2170322763598866</v>
+        <v>0.2172385150812065</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2842560832441753</v>
+        <v>0.2811323900217118</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2256054440065146</v>
+        <v>0.2275054440065146</v>
       </c>
       <c r="C93">
-        <v>-96.30565341663709</v>
+        <v>-99.02247372497825</v>
       </c>
       <c r="D93">
-        <v>76.79934658336293</v>
+        <v>76.23752627502176</v>
       </c>
       <c r="E93">
-        <v>181.105</v>
+        <v>183.26</v>
       </c>
       <c r="F93">
-        <v>196.105</v>
+        <v>198.26</v>
       </c>
       <c r="G93">
         <v>23</v>
@@ -8913,37 +8913,37 @@
         <v>13</v>
       </c>
       <c r="M93">
-        <v>46.24155900000001</v>
+        <v>46.74970800000001</v>
       </c>
       <c r="N93">
-        <v>-33.24155900000001</v>
+        <v>-33.74970800000001</v>
       </c>
       <c r="O93">
-        <v>-9.307636520000003</v>
+        <v>-9.449918240000002</v>
       </c>
       <c r="P93">
-        <v>-23.93392248000001</v>
+        <v>-24.29978976</v>
       </c>
       <c r="Q93">
-        <v>26.06607751999999</v>
+        <v>25.70021024</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.310204392029074</v>
+        <v>0.3432549410327084</v>
       </c>
       <c r="T93">
-        <v>6.106336998361988</v>
+        <v>6.869629123157238</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07871706920607931</v>
+        <v>0.07786144888862194</v>
       </c>
       <c r="W93">
-        <v>0.2172385150812065</v>
+        <v>0.217440270352063</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2811323900217118</v>
+        <v>0.2780766031736497</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2275054440065146</v>
+        <v>0.2294054440065146</v>
       </c>
       <c r="C94">
-        <v>-99.02247372497825</v>
+        <v>-101.731133813624</v>
       </c>
       <c r="D94">
-        <v>76.23752627502176</v>
+        <v>75.68386618637598</v>
       </c>
       <c r="E94">
-        <v>183.26</v>
+        <v>185.415</v>
       </c>
       <c r="F94">
-        <v>198.26</v>
+        <v>200.415</v>
       </c>
       <c r="G94">
         <v>23</v>
@@ -8995,37 +8995,37 @@
         <v>13</v>
       </c>
       <c r="M94">
-        <v>46.74970800000001</v>
+        <v>47.25785700000001</v>
       </c>
       <c r="N94">
-        <v>-33.74970800000001</v>
+        <v>-34.25785700000001</v>
       </c>
       <c r="O94">
-        <v>-9.449918240000002</v>
+        <v>-9.592199960000004</v>
       </c>
       <c r="P94">
-        <v>-24.29978976</v>
+        <v>-24.66565704000001</v>
       </c>
       <c r="Q94">
-        <v>25.70021024</v>
+        <v>25.33434295999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3432549410327084</v>
+        <v>0.385748504037381</v>
       </c>
       <c r="T94">
-        <v>6.869629123157238</v>
+        <v>7.851004712179701</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07786144888862194</v>
+        <v>0.07702422900809912</v>
       </c>
       <c r="W94">
-        <v>0.217440270352063</v>
+        <v>0.2176376867998902</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2780766031736497</v>
+        <v>0.2750865321717825</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2294054440065146</v>
+        <v>0.2313054440065146</v>
       </c>
       <c r="C95">
-        <v>-101.731133813624</v>
+        <v>-104.4318101867349</v>
       </c>
       <c r="D95">
-        <v>75.68386618637598</v>
+        <v>75.13818981326516</v>
       </c>
       <c r="E95">
-        <v>185.415</v>
+        <v>187.57</v>
       </c>
       <c r="F95">
-        <v>200.415</v>
+        <v>202.57</v>
       </c>
       <c r="G95">
         <v>23</v>
@@ -9077,37 +9077,37 @@
         <v>13</v>
       </c>
       <c r="M95">
-        <v>47.25785700000001</v>
+        <v>47.766006</v>
       </c>
       <c r="N95">
-        <v>-34.25785700000001</v>
+        <v>-34.766006</v>
       </c>
       <c r="O95">
-        <v>-9.592199960000004</v>
+        <v>-9.734481680000002</v>
       </c>
       <c r="P95">
-        <v>-24.66565704000001</v>
+        <v>-25.03152432</v>
       </c>
       <c r="Q95">
-        <v>25.33434295999999</v>
+        <v>24.96847568</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.385748504037381</v>
+        <v>0.4424065880436112</v>
       </c>
       <c r="T95">
-        <v>7.851004712179701</v>
+        <v>9.159505497542986</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07702422900809912</v>
+        <v>0.07620482231652359</v>
       </c>
       <c r="W95">
-        <v>0.2176376867998902</v>
+        <v>0.2178309028977637</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2750865321717825</v>
+        <v>0.27216007970187</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2313054440065146</v>
+        <v>0.2332054440065146</v>
       </c>
       <c r="C96">
-        <v>-104.4318101867349</v>
+        <v>-107.1246742945697</v>
       </c>
       <c r="D96">
-        <v>75.13818981326516</v>
+        <v>74.60032570543032</v>
       </c>
       <c r="E96">
-        <v>187.57</v>
+        <v>189.725</v>
       </c>
       <c r="F96">
-        <v>202.57</v>
+        <v>204.725</v>
       </c>
       <c r="G96">
         <v>23</v>
@@ -9159,37 +9159,37 @@
         <v>13</v>
       </c>
       <c r="M96">
-        <v>47.766006</v>
+        <v>48.27415500000001</v>
       </c>
       <c r="N96">
-        <v>-34.766006</v>
+        <v>-35.27415500000001</v>
       </c>
       <c r="O96">
-        <v>-9.734481680000002</v>
+        <v>-9.876763400000003</v>
       </c>
       <c r="P96">
-        <v>-25.03152432</v>
+        <v>-25.39739160000001</v>
       </c>
       <c r="Q96">
-        <v>24.96847568</v>
+        <v>24.60260839999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4424065880436112</v>
+        <v>0.5217279056523337</v>
       </c>
       <c r="T96">
-        <v>9.159505497542986</v>
+        <v>10.99140659705159</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07620482231652359</v>
+        <v>0.07540266629213913</v>
       </c>
       <c r="W96">
-        <v>0.2178309028977637</v>
+        <v>0.2180200512883136</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.27216007970187</v>
+        <v>0.2692952367576398</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2332054440065146</v>
+        <v>0.2351054440065146</v>
       </c>
       <c r="C97">
-        <v>-107.1246742945697</v>
+        <v>-109.8098927130878</v>
       </c>
       <c r="D97">
-        <v>74.60032570543032</v>
+        <v>74.07010728691218</v>
       </c>
       <c r="E97">
-        <v>189.725</v>
+        <v>191.88</v>
       </c>
       <c r="F97">
-        <v>204.725</v>
+        <v>206.88</v>
       </c>
       <c r="G97">
         <v>23</v>
@@ -9241,37 +9241,37 @@
         <v>13</v>
       </c>
       <c r="M97">
-        <v>48.27415500000001</v>
+        <v>48.78230400000001</v>
       </c>
       <c r="N97">
-        <v>-35.27415500000001</v>
+        <v>-35.78230400000001</v>
       </c>
       <c r="O97">
-        <v>-9.876763400000003</v>
+        <v>-10.01904512</v>
       </c>
       <c r="P97">
-        <v>-25.39739160000001</v>
+        <v>-25.76325888000001</v>
       </c>
       <c r="Q97">
-        <v>24.60260839999999</v>
+        <v>24.23674111999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5217279056523337</v>
+        <v>0.6407098820654175</v>
       </c>
       <c r="T97">
-        <v>10.99140659705159</v>
+        <v>13.73925824631449</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07540266629213913</v>
+        <v>0.074617221851596</v>
       </c>
       <c r="W97">
-        <v>0.2180200512883136</v>
+        <v>0.2182052590873937</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2692952367576398</v>
+        <v>0.2664900780414143</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2351054440065146</v>
+        <v>0.2370054440065146</v>
       </c>
       <c r="C98">
-        <v>-109.8098927130878</v>
+        <v>-112.4876273159458</v>
       </c>
       <c r="D98">
-        <v>74.07010728691222</v>
+        <v>73.54737268405421</v>
       </c>
       <c r="E98">
-        <v>191.88</v>
+        <v>194.035</v>
       </c>
       <c r="F98">
-        <v>206.88</v>
+        <v>209.035</v>
       </c>
       <c r="G98">
         <v>23</v>
@@ -9323,37 +9323,37 @@
         <v>13</v>
       </c>
       <c r="M98">
-        <v>48.782304</v>
+        <v>49.290453</v>
       </c>
       <c r="N98">
-        <v>-35.782304</v>
+        <v>-36.290453</v>
       </c>
       <c r="O98">
-        <v>-10.01904512</v>
+        <v>-10.16132684</v>
       </c>
       <c r="P98">
-        <v>-25.76325888</v>
+        <v>-26.12912616</v>
       </c>
       <c r="Q98">
-        <v>24.23674112</v>
+        <v>23.87087384</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6407098820654158</v>
+        <v>0.8390131760872211</v>
       </c>
       <c r="T98">
-        <v>13.73925824631446</v>
+        <v>18.31901099508594</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07461722185159603</v>
+        <v>0.07384797214178576</v>
       </c>
       <c r="W98">
-        <v>0.2182052590873937</v>
+        <v>0.2183866481689669</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2664900780414143</v>
+        <v>0.2637427576492348</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2370054440065146</v>
+        <v>0.2389054440065146</v>
       </c>
       <c r="C99">
-        <v>-112.4876273159458</v>
+        <v>-115.1580354392622</v>
       </c>
       <c r="D99">
-        <v>73.54737268405421</v>
+        <v>73.0319645607378</v>
       </c>
       <c r="E99">
-        <v>194.035</v>
+        <v>196.19</v>
       </c>
       <c r="F99">
-        <v>209.035</v>
+        <v>211.19</v>
       </c>
       <c r="G99">
         <v>23</v>
@@ -9405,37 +9405,37 @@
         <v>13</v>
       </c>
       <c r="M99">
-        <v>49.290453</v>
+        <v>49.798602</v>
       </c>
       <c r="N99">
-        <v>-36.290453</v>
+        <v>-36.798602</v>
       </c>
       <c r="O99">
-        <v>-10.16132684</v>
+        <v>-10.30360856</v>
       </c>
       <c r="P99">
-        <v>-26.12912616</v>
+        <v>-26.49499344</v>
       </c>
       <c r="Q99">
-        <v>23.87087384</v>
+        <v>23.50500656</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8390131760872211</v>
+        <v>1.235619764130832</v>
       </c>
       <c r="T99">
-        <v>18.31901099508594</v>
+        <v>27.47851649262892</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07384797214178576</v>
+        <v>0.07309442140564509</v>
       </c>
       <c r="W99">
-        <v>0.2183866481689669</v>
+        <v>0.2185643354325489</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2637427576492348</v>
+        <v>0.2610515050201609</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2389054440065146</v>
+        <v>0.2408054440065146</v>
       </c>
       <c r="C100">
-        <v>-115.1580354392622</v>
+        <v>-117.8212700395031</v>
       </c>
       <c r="D100">
-        <v>73.0319645607378</v>
+        <v>72.52372996049692</v>
       </c>
       <c r="E100">
-        <v>196.19</v>
+        <v>198.345</v>
       </c>
       <c r="F100">
-        <v>211.19</v>
+        <v>213.345</v>
       </c>
       <c r="G100">
         <v>23</v>
@@ -9487,37 +9487,37 @@
         <v>13</v>
       </c>
       <c r="M100">
-        <v>49.798602</v>
+        <v>50.306751</v>
       </c>
       <c r="N100">
-        <v>-36.798602</v>
+        <v>-37.306751</v>
       </c>
       <c r="O100">
-        <v>-10.30360856</v>
+        <v>-10.44589028</v>
       </c>
       <c r="P100">
-        <v>-26.49499344</v>
+        <v>-26.86086072</v>
       </c>
       <c r="Q100">
-        <v>23.50500656</v>
+        <v>23.13913928</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.235619764130832</v>
+        <v>2.425439528261663</v>
       </c>
       <c r="T100">
-        <v>27.47851649262892</v>
+        <v>54.95703298525783</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07309442140564509</v>
+        <v>0.07235609391669919</v>
       </c>
       <c r="W100">
-        <v>0.2185643354325489</v>
+        <v>0.2187384330544423</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2610515050201609</v>
+        <v>0.2584146211310685</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2408054440065146</v>
-      </c>
-      <c r="C101">
-        <v>-117.8212700395031</v>
-      </c>
-      <c r="D101">
-        <v>72.52372996049692</v>
-      </c>
-      <c r="E101">
-        <v>198.345</v>
-      </c>
-      <c r="F101">
-        <v>213.345</v>
-      </c>
-      <c r="G101">
-        <v>23</v>
-      </c>
-      <c r="H101">
-        <v>200.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63</v>
-      </c>
-      <c r="K101">
-        <v>50</v>
-      </c>
-      <c r="L101">
-        <v>13</v>
-      </c>
-      <c r="M101">
-        <v>50.306751</v>
-      </c>
-      <c r="N101">
-        <v>-37.306751</v>
-      </c>
-      <c r="O101">
-        <v>-10.44589028</v>
-      </c>
-      <c r="P101">
-        <v>-26.86086072</v>
-      </c>
-      <c r="Q101">
-        <v>23.13913928</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.425439528261663</v>
-      </c>
-      <c r="T101">
-        <v>54.95703298525783</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07235609391669919</v>
-      </c>
-      <c r="W101">
-        <v>0.2187384330544423</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2584146211310685</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
